--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="204">
   <si>
     <t>Conference name</t>
   </si>
@@ -59,18 +59,36 @@
     <t>Soft penalty per missing preferred tag in a talk's timeslot</t>
   </si>
   <si>
+    <t>Speaker undesired timeslot tag</t>
+  </si>
+  <si>
+    <t>Soft penalty per undesired tag in a talk's timeslot</t>
+  </si>
+  <si>
     <t>Talk preferred timeslot tag</t>
   </si>
   <si>
+    <t>Talk undesired timeslot tag</t>
+  </si>
+  <si>
     <t>Speaker preferred room tag</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's room</t>
   </si>
   <si>
+    <t>Speaker undesired room tag</t>
+  </si>
+  <si>
+    <t>Soft penalty per undesired tag in a talk's room</t>
+  </si>
+  <si>
     <t>Talk preferred room tag</t>
   </si>
   <si>
+    <t>Talk undesired room tag</t>
+  </si>
+  <si>
     <t>Day</t>
   </si>
   <si>
@@ -185,10 +203,22 @@
     <t>Preferred timeslot tags</t>
   </si>
   <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
     <t>Required room tags</t>
   </si>
   <si>
     <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
   </si>
   <si>
     <t>Amy Cole</t>
@@ -668,9 +698,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.0859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="23.85546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="70.88671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.8671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.69921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="81.296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,18 +775,18 @@
         <v>10.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
         <v>10.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -767,7 +797,51 @@
         <v>10.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -780,232 +854,232 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="9.41796875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="5.1484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.14453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.3984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.32421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.78515625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
         <v>36</v>
       </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1018,328 +1092,328 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="6.48828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="25.6328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.3125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1356,1407 +1430,1723 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.69921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.09765625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="19.07421875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="19.47265625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.85546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="25.390625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="26.30859375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="26.0234375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="21.671875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="22.20703125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="23.125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="22.84375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q5" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q6" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q8" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q10" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" t="s">
+        <v>32</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P11" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q12" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" t="s">
+        <v>32</v>
+      </c>
+      <c r="U12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K13" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q13" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
+        <v>32</v>
+      </c>
+      <c r="S13" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" t="s">
+        <v>32</v>
+      </c>
+      <c r="U13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q14" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14" t="s">
+        <v>32</v>
+      </c>
+      <c r="U14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q15" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R15" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q16" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R16" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" t="s">
+        <v>32</v>
+      </c>
+      <c r="U16" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q17" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R17" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" t="s">
+        <v>32</v>
+      </c>
+      <c r="U17" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q18" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R18" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q19" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R19" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" t="s">
+        <v>32</v>
+      </c>
+      <c r="U19" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q20" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R20" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q21" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" t="s">
+        <v>32</v>
+      </c>
+      <c r="U21" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
       </c>
       <c r="I22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="P22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q22" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q23" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R23" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" t="s">
+        <v>32</v>
+      </c>
+      <c r="U23" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q24" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R24" t="s">
+        <v>32</v>
+      </c>
+      <c r="S24" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" t="s">
+        <v>32</v>
+      </c>
+      <c r="U24" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q25" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R25" t="s">
+        <v>32</v>
+      </c>
+      <c r="S25" t="s">
+        <v>32</v>
+      </c>
+      <c r="T25" t="s">
+        <v>32</v>
+      </c>
+      <c r="U25" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q26" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="R26" t="s">
+        <v>32</v>
+      </c>
+      <c r="S26" t="s">
+        <v>32</v>
+      </c>
+      <c r="T26" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="P1:U1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -2767,1872 +3157,2320 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.41796875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="20.3046875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.515625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="9.7109375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="22.85546875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="21.69921875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="22.09765625" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="19.07421875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="19.47265625" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="14.578125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.99609375" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="6.44921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.20703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.78515625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="19.8203125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="17.30859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.3046875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="24.015625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="24.85546875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="25.390625" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="26.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="26.0234375" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="21.671875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="22.20703125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="23.125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="22.84375" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="16.65234375" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="16.14453125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="6.3984375" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="6.32421875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.02734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" t="b">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="b">
         <v>0</v>
       </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" t="s">
-        <v>26</v>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" t="b">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="b">
         <v>0</v>
       </c>
-      <c r="M3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" t="s">
-        <v>26</v>
+      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" t="b">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="b">
         <v>0</v>
       </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" t="s">
-        <v>26</v>
+      <c r="Q4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
         <v>103</v>
       </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
         <v>104</v>
       </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="b">
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="b">
         <v>0</v>
       </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" t="s">
-        <v>26</v>
+      <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" t="b">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" t="s">
-        <v>26</v>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" t="b">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="b">
         <v>0</v>
       </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" t="s">
-        <v>26</v>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" t="b">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="b">
         <v>0</v>
       </c>
-      <c r="M8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" t="s">
-        <v>26</v>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" t="b">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="b">
         <v>0</v>
       </c>
-      <c r="M9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" t="s">
-        <v>26</v>
+      <c r="Q9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" t="b">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="b">
         <v>0</v>
       </c>
-      <c r="M10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P10" t="s">
-        <v>26</v>
+      <c r="Q10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="b">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P11" t="s">
-        <v>26</v>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
         <v>125</v>
       </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>115</v>
-      </c>
       <c r="F12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" t="b">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" t="b">
         <v>0</v>
       </c>
-      <c r="M12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" t="s">
-        <v>26</v>
-      </c>
-      <c r="P12" t="s">
-        <v>26</v>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" t="b">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" t="b">
         <v>0</v>
       </c>
-      <c r="M13" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" t="s">
-        <v>26</v>
-      </c>
-      <c r="P13" t="s">
-        <v>26</v>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
+        <v>32</v>
+      </c>
+      <c r="S13" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="b">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" t="b">
         <v>0</v>
       </c>
-      <c r="M14" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" t="s">
-        <v>26</v>
-      </c>
-      <c r="P14" t="s">
-        <v>26</v>
+      <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
         <v>133</v>
       </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G15" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="b">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" t="s">
-        <v>26</v>
-      </c>
-      <c r="P15" t="s">
-        <v>26</v>
+      <c r="Q15" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" t="b">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" t="b">
         <v>0</v>
       </c>
-      <c r="M16" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" t="s">
-        <v>26</v>
-      </c>
-      <c r="P16" t="s">
-        <v>26</v>
+      <c r="Q16" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" t="b">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" t="b">
         <v>0</v>
       </c>
-      <c r="M17" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" t="s">
-        <v>26</v>
-      </c>
-      <c r="P17" t="s">
-        <v>26</v>
+      <c r="Q17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
         <v>141</v>
       </c>
-      <c r="B18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>131</v>
-      </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G18" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="b">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" t="b">
         <v>0</v>
       </c>
-      <c r="M18" t="s">
-        <v>26</v>
-      </c>
-      <c r="N18" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" t="s">
-        <v>26</v>
-      </c>
-      <c r="P18" t="s">
-        <v>26</v>
+      <c r="Q18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K19" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" t="b">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" t="b">
         <v>0</v>
       </c>
-      <c r="M19" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" t="s">
-        <v>26</v>
-      </c>
-      <c r="P19" t="s">
-        <v>26</v>
+      <c r="Q19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K20" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" t="b">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" t="b">
         <v>0</v>
       </c>
-      <c r="M20" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" t="s">
-        <v>26</v>
-      </c>
-      <c r="P20" t="s">
-        <v>26</v>
+      <c r="Q20" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K21" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" t="b">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" t="s">
+        <v>32</v>
+      </c>
+      <c r="O21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" t="b">
         <v>0</v>
       </c>
-      <c r="M21" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P21" t="s">
-        <v>26</v>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G22" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K22" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" t="b">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" t="b">
         <v>0</v>
       </c>
-      <c r="M22" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" t="s">
-        <v>26</v>
-      </c>
-      <c r="P22" t="s">
-        <v>26</v>
+      <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" t="b">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" t="s">
+        <v>32</v>
+      </c>
+      <c r="P23" t="b">
         <v>0</v>
       </c>
-      <c r="M23" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" t="s">
-        <v>26</v>
-      </c>
-      <c r="P23" t="s">
-        <v>26</v>
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" t="b">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" t="s">
+        <v>32</v>
+      </c>
+      <c r="O24" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" t="b">
         <v>0</v>
       </c>
-      <c r="M24" t="s">
-        <v>26</v>
-      </c>
-      <c r="N24" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" t="s">
-        <v>26</v>
-      </c>
-      <c r="P24" t="s">
-        <v>26</v>
+      <c r="Q24" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" t="s">
+        <v>32</v>
+      </c>
+      <c r="S24" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" t="s">
+        <v>32</v>
+      </c>
+      <c r="P25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="s">
         <v>28</v>
       </c>
-      <c r="D25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" t="s">
-        <v>23</v>
-      </c>
-      <c r="O25" t="s">
-        <v>27</v>
-      </c>
-      <c r="P25" t="s">
-        <v>44</v>
+      <c r="R25" t="s">
+        <v>29</v>
+      </c>
+      <c r="S25" t="s">
+        <v>33</v>
+      </c>
+      <c r="T25" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" t="b">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" t="s">
+        <v>32</v>
+      </c>
+      <c r="O26" t="s">
+        <v>32</v>
+      </c>
+      <c r="P26" t="b">
         <v>0</v>
       </c>
-      <c r="M26" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" t="s">
-        <v>26</v>
-      </c>
-      <c r="P26" t="s">
-        <v>26</v>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" t="s">
+        <v>32</v>
+      </c>
+      <c r="S26" t="s">
+        <v>32</v>
+      </c>
+      <c r="T26" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" t="b">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" t="s">
+        <v>32</v>
+      </c>
+      <c r="O27" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" t="b">
         <v>0</v>
       </c>
-      <c r="M27" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" t="s">
-        <v>26</v>
-      </c>
-      <c r="O27" t="s">
-        <v>26</v>
-      </c>
-      <c r="P27" t="s">
-        <v>26</v>
+      <c r="Q27" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" t="s">
+        <v>32</v>
+      </c>
+      <c r="S27" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G28" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K28" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" t="b">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" t="s">
+        <v>32</v>
+      </c>
+      <c r="P28" t="b">
         <v>0</v>
       </c>
-      <c r="M28" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" t="s">
-        <v>26</v>
-      </c>
-      <c r="P28" t="s">
-        <v>26</v>
+      <c r="Q28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" t="s">
+        <v>32</v>
+      </c>
+      <c r="T28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G29" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" t="b">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" t="s">
+        <v>32</v>
+      </c>
+      <c r="O29" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" t="b">
         <v>0</v>
       </c>
-      <c r="M29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" t="s">
-        <v>26</v>
-      </c>
-      <c r="O29" t="s">
-        <v>26</v>
-      </c>
-      <c r="P29" t="s">
-        <v>26</v>
+      <c r="Q29" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" t="s">
+        <v>32</v>
+      </c>
+      <c r="S29" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K30" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" t="b">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" t="s">
+        <v>32</v>
+      </c>
+      <c r="O30" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" t="b">
         <v>0</v>
       </c>
-      <c r="M30" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" t="s">
-        <v>26</v>
-      </c>
-      <c r="P30" t="s">
-        <v>26</v>
+      <c r="Q30" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" t="s">
+        <v>32</v>
+      </c>
+      <c r="T30" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G31" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K31" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" t="b">
+        <v>32</v>
+      </c>
+      <c r="L31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" t="s">
+        <v>32</v>
+      </c>
+      <c r="O31" t="s">
+        <v>32</v>
+      </c>
+      <c r="P31" t="b">
         <v>0</v>
       </c>
-      <c r="M31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" t="s">
-        <v>26</v>
-      </c>
-      <c r="P31" t="s">
-        <v>26</v>
+      <c r="Q31" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" t="s">
+        <v>32</v>
+      </c>
+      <c r="T31" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I32" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" t="b">
+        <v>32</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" t="s">
+        <v>32</v>
+      </c>
+      <c r="N32" t="s">
+        <v>32</v>
+      </c>
+      <c r="O32" t="s">
+        <v>32</v>
+      </c>
+      <c r="P32" t="b">
         <v>0</v>
       </c>
-      <c r="M32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" t="s">
-        <v>26</v>
-      </c>
-      <c r="P32" t="s">
-        <v>26</v>
+      <c r="Q32" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" t="s">
+        <v>32</v>
+      </c>
+      <c r="S32" t="s">
+        <v>32</v>
+      </c>
+      <c r="T32" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G33" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I33" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K33" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" t="b">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" t="s">
+        <v>32</v>
+      </c>
+      <c r="O33" t="s">
+        <v>32</v>
+      </c>
+      <c r="P33" t="b">
         <v>0</v>
       </c>
-      <c r="M33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" t="s">
-        <v>26</v>
-      </c>
-      <c r="P33" t="s">
-        <v>26</v>
+      <c r="Q33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" t="s">
+        <v>32</v>
+      </c>
+      <c r="S33" t="s">
+        <v>32</v>
+      </c>
+      <c r="T33" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G34" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I34" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" t="b">
+        <v>32</v>
+      </c>
+      <c r="L34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P34" t="b">
         <v>0</v>
       </c>
-      <c r="M34" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" t="s">
-        <v>26</v>
-      </c>
-      <c r="O34" t="s">
-        <v>26</v>
-      </c>
-      <c r="P34" t="s">
-        <v>26</v>
+      <c r="Q34" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" t="s">
+        <v>32</v>
+      </c>
+      <c r="T34" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G35" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H35" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I35" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K35" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" t="b">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" t="b">
         <v>0</v>
       </c>
-      <c r="M35" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" t="s">
-        <v>26</v>
-      </c>
-      <c r="P35" t="s">
-        <v>26</v>
+      <c r="Q35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" t="s">
+        <v>32</v>
+      </c>
+      <c r="S35" t="s">
+        <v>32</v>
+      </c>
+      <c r="T35" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G36" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K36" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" t="b">
+        <v>32</v>
+      </c>
+      <c r="L36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" t="b">
         <v>0</v>
       </c>
-      <c r="M36" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" t="s">
-        <v>26</v>
-      </c>
-      <c r="P36" t="s">
-        <v>26</v>
+      <c r="Q36" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" t="s">
+        <v>32</v>
+      </c>
+      <c r="S36" t="s">
+        <v>32</v>
+      </c>
+      <c r="T36" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K37" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" t="b">
+        <v>32</v>
+      </c>
+      <c r="L37" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" t="s">
+        <v>32</v>
+      </c>
+      <c r="O37" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" t="b">
         <v>0</v>
       </c>
-      <c r="M37" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" t="s">
-        <v>26</v>
-      </c>
-      <c r="P37" t="s">
-        <v>26</v>
+      <c r="Q37" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" t="s">
+        <v>32</v>
+      </c>
+      <c r="S37" t="s">
+        <v>32</v>
+      </c>
+      <c r="T37" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -4645,142 +5483,142 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.71875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="12.203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -4798,101 +5636,101 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -13,12 +13,13 @@
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
     <sheet name="Theme view" r:id="rId8" sheetId="6"/>
     <sheet name="Sector view" r:id="rId9" sheetId="7"/>
+    <sheet name="Speaker view" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="231">
   <si>
     <t>Conference name</t>
   </si>
@@ -176,460 +177,541 @@
     <t>Large, Recorded</t>
   </si>
   <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Theme tags</t>
+  </si>
+  <si>
+    <t>Sector tags</t>
+  </si>
+  <si>
+    <t>Audience level</t>
+  </si>
+  <si>
+    <t>Content tags</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Pinned by user</t>
+  </si>
+  <si>
+    <t>Timeslot day</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>S00</t>
+  </si>
+  <si>
+    <t>Hands on real-time OpenShift</t>
+  </si>
+  <si>
+    <t>Amy Cole, Beth Fox</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>OpenShift</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>Lab_room</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Dan Jones, Elsa King</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Flo Li, Gus Poe</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Middleware, Cloud</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Cloud, Modern Web</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Culture, Mobile</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Ivy Watt, Jay Cole</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Security, Middleware</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Beth Fox, Chad Green</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
     <t>S23</t>
   </si>
   <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Theme tags</t>
-  </si>
-  <si>
-    <t>Sector tags</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Speakers</t>
-  </si>
-  <si>
-    <t>Pinned by user</t>
-  </si>
-  <si>
-    <t>Timeslot day</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>S00</t>
-  </si>
-  <si>
-    <t>Hands on real-time OpenShift</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Modern Web, IoT</t>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>Hugo Rye, Ivy Smith</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>Jay Watt, Amy Fox</t>
+  </si>
+  <si>
+    <t>Mobile, Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>Beth Green, Chad Jones</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Culture</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
+    <t>Cloud, Big Data</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>Gus Rye, Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
+    <t>Jay Cole, Amy Green</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Applying modern Weld</t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Grok distributed RestEasy</t>
+  </si>
+  <si>
+    <t>Dan Li, Amy Cole</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Android</t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Using secure Tensorflow</t>
   </si>
   <si>
     <t>Chad Green, Dan Jones</t>
   </si>
   <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Elsa King, Flo Li</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise JUnit</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Beth Green, Chad Jones</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>Gus Rye, Hugo Smith</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>Ivy Watt, Jay Cole</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>IoT, Modern Web</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Beth Jones, Chad King</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>Dan Li, Amy Cole</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Securing scalable JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Debug enterprise OpenShift</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time Spring</t>
-  </si>
-  <si>
-    <t>Modern Web, Cloud</t>
-  </si>
-  <si>
-    <t>Elsa King, Flo Li, Gus Poe</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Drools</t>
-  </si>
-  <si>
-    <t>Hugo Rye, Ivy Smith</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized OptaPlanner</t>
-  </si>
-  <si>
-    <t>Intro to serverless jBPM</t>
-  </si>
-  <si>
-    <t>Amy Fox, Beth Green</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven Camel</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning XStream</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Docker</t>
-  </si>
-  <si>
-    <t>Elsa Li, Flo Poe</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning JUnit</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable OpenShift</t>
-  </si>
-  <si>
-    <t>Modern Web, Mobile</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise WildFly</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Hands on real-time Drools</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>Advanced containerized OptaPlanner</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>Learn virtualized jBPM</t>
-  </si>
-  <si>
-    <t>Big Data, Mobile</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>Intro to serverless Camel</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>Discover AI-driven XStream</t>
-  </si>
-  <si>
-    <t>Beth Fox, Chad Green</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Docker</t>
-  </si>
-  <si>
     <t>Theme tag</t>
   </si>
   <si>
     <t>Sector tag</t>
+  </si>
+  <si>
+    <t>Speaker</t>
   </si>
 </sst>
 </file>
@@ -651,7 +733,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,6 +753,16 @@
         <fgColor rgb="AD7FA8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="EF2929"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCAF3E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -684,11 +776,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -698,9 +792,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.8671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.69921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="81.296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="29.5" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.85546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="70.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -854,11 +948,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.14453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="6.078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="9.41796875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="5.1484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1092,20 +1186,20 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.3125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="6.48828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.6328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1430,27 +1524,27 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.85546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.390625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="26.30859375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="26.0234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="21.671875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="22.20703125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="23.125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="22.84375" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="21.69921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="22.09765625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="23.01171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="22.7734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="19.07421875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="19.47265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="20.3828125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="20.1484375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1875,7 +1969,7 @@
         <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L7" t="s">
         <v>32</v>
@@ -2265,7 +2359,7 @@
         <v>32</v>
       </c>
       <c r="K13" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
         <v>32</v>
@@ -2330,7 +2424,7 @@
         <v>32</v>
       </c>
       <c r="K14" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="L14" t="s">
         <v>32</v>
@@ -3157,26 +3251,28 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.20703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="19.8203125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="17.30859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.3046875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="24.015625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="24.85546875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="25.390625" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="26.30859375" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="26.0234375" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.671875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.20703125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="23.125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="22.84375" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="16.65234375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="16.14453125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.02734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.69140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.7734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.41796875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="28.2265625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="26.98828125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="16.515625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="14.4375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6640625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="9.7109375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="21.69921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="22.09765625" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="23.01171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="22.7734375" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="19.07421875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="19.47265625" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="20.3828125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="20.1484375" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="14.578125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="15.99609375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="6.44921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3202,72 +3298,78 @@
         <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>99</v>
+      <c r="V1" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" t="s">
-        <v>67</v>
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.0</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J2" t="s">
         <v>32</v>
@@ -3276,61 +3378,67 @@
         <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
         <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="O2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="b">
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" t="b">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" t="s">
-        <v>32</v>
-      </c>
       <c r="S2" t="s">
         <v>32</v>
       </c>
       <c r="T2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
       </c>
       <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" t="s">
         <v>107</v>
       </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
       <c r="J3" t="s">
         <v>32</v>
       </c>
@@ -3338,60 +3446,66 @@
         <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
         <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="O3" t="s">
         <v>32</v>
       </c>
-      <c r="P3" t="b">
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="b">
         <v>0</v>
       </c>
-      <c r="Q3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" t="s">
-        <v>32</v>
-      </c>
       <c r="S3" t="s">
         <v>32</v>
       </c>
       <c r="T3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G4" t="s">
-        <v>111</v>
+        <v>32</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.0</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
@@ -3400,60 +3514,66 @@
         <v>32</v>
       </c>
       <c r="L4" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
         <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="O4" t="s">
         <v>32</v>
       </c>
-      <c r="P4" t="b">
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" t="b">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" t="s">
-        <v>32</v>
-      </c>
       <c r="S4" t="s">
         <v>32</v>
       </c>
       <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" t="s">
-        <v>115</v>
+        <v>123</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.0</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J5" t="s">
         <v>32</v>
@@ -3462,60 +3582,66 @@
         <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
         <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
       </c>
-      <c r="P5" t="b">
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="b">
         <v>0</v>
       </c>
-      <c r="Q5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" t="s">
-        <v>32</v>
-      </c>
       <c r="S5" t="s">
         <v>32</v>
       </c>
       <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.0</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
         <v>32</v>
@@ -3535,49 +3661,55 @@
       <c r="O6" t="s">
         <v>32</v>
       </c>
-      <c r="P6" t="b">
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="b">
         <v>0</v>
       </c>
-      <c r="Q6" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" t="s">
-        <v>32</v>
-      </c>
       <c r="S6" t="s">
         <v>32</v>
       </c>
       <c r="T6" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" t="s">
-        <v>74</v>
+        <v>32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.0</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J7" t="s">
         <v>32</v>
@@ -3597,49 +3729,55 @@
       <c r="O7" t="s">
         <v>32</v>
       </c>
-      <c r="P7" t="b">
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" t="b">
         <v>0</v>
       </c>
-      <c r="Q7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R7" t="s">
-        <v>32</v>
-      </c>
       <c r="S7" t="s">
         <v>32</v>
       </c>
       <c r="T7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>32</v>
+      </c>
+      <c r="V7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" t="s">
-        <v>75</v>
+        <v>32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.0</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J8" t="s">
         <v>32</v>
@@ -3659,49 +3797,55 @@
       <c r="O8" t="s">
         <v>32</v>
       </c>
-      <c r="P8" t="b">
+      <c r="P8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="b">
         <v>0</v>
       </c>
-      <c r="Q8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" t="s">
-        <v>32</v>
-      </c>
       <c r="S8" t="s">
         <v>32</v>
       </c>
       <c r="T8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8" t="s">
+        <v>32</v>
+      </c>
+      <c r="V8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9" t="s">
-        <v>76</v>
+        <v>32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.0</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J9" t="s">
         <v>32</v>
@@ -3721,49 +3865,55 @@
       <c r="O9" t="s">
         <v>32</v>
       </c>
-      <c r="P9" t="b">
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="b">
         <v>0</v>
       </c>
-      <c r="Q9" t="s">
-        <v>32</v>
-      </c>
-      <c r="R9" t="s">
-        <v>32</v>
-      </c>
       <c r="S9" t="s">
         <v>32</v>
       </c>
       <c r="T9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" t="s">
+        <v>32</v>
+      </c>
+      <c r="V9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
       </c>
       <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
         <v>130</v>
       </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
       <c r="F10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" t="s">
-        <v>77</v>
+        <v>32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.0</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J10" t="s">
         <v>32</v>
@@ -3783,49 +3933,55 @@
       <c r="O10" t="s">
         <v>32</v>
       </c>
-      <c r="P10" t="b">
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" t="b">
         <v>0</v>
       </c>
-      <c r="Q10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" t="s">
-        <v>32</v>
-      </c>
       <c r="S10" t="s">
         <v>32</v>
       </c>
       <c r="T10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U10" t="s">
+        <v>32</v>
+      </c>
+      <c r="V10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s">
         <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" t="s">
-        <v>134</v>
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.0</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -3845,49 +4001,55 @@
       <c r="O11" t="s">
         <v>32</v>
       </c>
-      <c r="P11" t="b">
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="b">
         <v>0</v>
       </c>
-      <c r="Q11" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" t="s">
-        <v>32</v>
-      </c>
       <c r="S11" t="s">
         <v>32</v>
       </c>
       <c r="T11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U11" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" t="s">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.0</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J12" t="s">
         <v>32</v>
@@ -3907,49 +4069,55 @@
       <c r="O12" t="s">
         <v>32</v>
       </c>
-      <c r="P12" t="b">
+      <c r="P12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" t="b">
         <v>0</v>
       </c>
-      <c r="Q12" t="s">
-        <v>32</v>
-      </c>
-      <c r="R12" t="s">
-        <v>32</v>
-      </c>
       <c r="S12" t="s">
         <v>32</v>
       </c>
       <c r="T12" t="s">
+        <v>32</v>
+      </c>
+      <c r="U12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" t="s">
-        <v>81</v>
+        <v>32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.0</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -3969,49 +4137,55 @@
       <c r="O13" t="s">
         <v>32</v>
       </c>
-      <c r="P13" t="b">
+      <c r="P13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="b">
         <v>0</v>
       </c>
-      <c r="Q13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" t="s">
-        <v>32</v>
-      </c>
       <c r="S13" t="s">
         <v>32</v>
       </c>
       <c r="T13" t="s">
+        <v>32</v>
+      </c>
+      <c r="U13" t="s">
+        <v>32</v>
+      </c>
+      <c r="V13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" t="s">
-        <v>82</v>
+        <v>32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.0</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -4031,49 +4205,55 @@
       <c r="O14" t="s">
         <v>32</v>
       </c>
-      <c r="P14" t="b">
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="b">
         <v>0</v>
       </c>
-      <c r="Q14" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" t="s">
-        <v>32</v>
-      </c>
       <c r="S14" t="s">
         <v>32</v>
       </c>
       <c r="T14" t="s">
+        <v>32</v>
+      </c>
+      <c r="U14" t="s">
+        <v>32</v>
+      </c>
+      <c r="V14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
-      </c>
-      <c r="G15" t="s">
-        <v>144</v>
+        <v>32</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.0</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>161</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -4093,49 +4273,55 @@
       <c r="O15" t="s">
         <v>32</v>
       </c>
-      <c r="P15" t="b">
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" t="b">
         <v>0</v>
       </c>
-      <c r="Q15" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" t="s">
-        <v>32</v>
-      </c>
       <c r="S15" t="s">
         <v>32</v>
       </c>
       <c r="T15" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C16" t="s">
         <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" t="s">
-        <v>147</v>
+        <v>32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.0</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -4155,49 +4341,55 @@
       <c r="O16" t="s">
         <v>32</v>
       </c>
-      <c r="P16" t="b">
+      <c r="P16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" t="b">
         <v>0</v>
       </c>
-      <c r="Q16" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" t="s">
-        <v>32</v>
-      </c>
       <c r="S16" t="s">
         <v>32</v>
       </c>
       <c r="T16" t="s">
+        <v>32</v>
+      </c>
+      <c r="U16" t="s">
+        <v>32</v>
+      </c>
+      <c r="V16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
         <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
-      </c>
-      <c r="G17" t="s">
-        <v>87</v>
+        <v>32</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.0</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>169</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J17" t="s">
         <v>32</v>
@@ -4217,49 +4409,55 @@
       <c r="O17" t="s">
         <v>32</v>
       </c>
-      <c r="P17" t="b">
+      <c r="P17" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="b">
         <v>0</v>
       </c>
-      <c r="Q17" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" t="s">
-        <v>32</v>
-      </c>
       <c r="S17" t="s">
         <v>32</v>
       </c>
       <c r="T17" t="s">
+        <v>32</v>
+      </c>
+      <c r="U17" t="s">
+        <v>32</v>
+      </c>
+      <c r="V17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
-      </c>
-      <c r="G18" t="s">
-        <v>153</v>
+        <v>32</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.0</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -4279,50 +4477,56 @@
       <c r="O18" t="s">
         <v>32</v>
       </c>
-      <c r="P18" t="b">
+      <c r="P18" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" t="b">
         <v>0</v>
       </c>
-      <c r="Q18" t="s">
-        <v>32</v>
-      </c>
-      <c r="R18" t="s">
-        <v>32</v>
-      </c>
       <c r="S18" t="s">
         <v>32</v>
       </c>
       <c r="T18" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" t="s">
+        <v>32</v>
+      </c>
+      <c r="V18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="I19" t="s">
         <v>107</v>
       </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" t="s">
-        <v>156</v>
-      </c>
-      <c r="H19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" t="s">
-        <v>32</v>
-      </c>
       <c r="J19" t="s">
         <v>32</v>
       </c>
@@ -4341,49 +4545,55 @@
       <c r="O19" t="s">
         <v>32</v>
       </c>
-      <c r="P19" t="b">
+      <c r="P19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" t="b">
         <v>0</v>
       </c>
-      <c r="Q19" t="s">
-        <v>32</v>
-      </c>
-      <c r="R19" t="s">
-        <v>32</v>
-      </c>
       <c r="S19" t="s">
         <v>32</v>
       </c>
       <c r="T19" t="s">
+        <v>32</v>
+      </c>
+      <c r="U19" t="s">
+        <v>32</v>
+      </c>
+      <c r="V19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" t="s">
-        <v>68</v>
+        <v>180</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.0</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -4403,49 +4613,55 @@
       <c r="O20" t="s">
         <v>32</v>
       </c>
-      <c r="P20" t="b">
+      <c r="P20" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" t="b">
         <v>0</v>
       </c>
-      <c r="Q20" t="s">
-        <v>32</v>
-      </c>
-      <c r="R20" t="s">
-        <v>32</v>
-      </c>
       <c r="S20" t="s">
         <v>32</v>
       </c>
       <c r="T20" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C21" t="s">
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="F21" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" t="s">
-        <v>111</v>
+        <v>32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.0</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -4465,49 +4681,55 @@
       <c r="O21" t="s">
         <v>32</v>
       </c>
-      <c r="P21" t="b">
+      <c r="P21" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" t="b">
         <v>0</v>
       </c>
-      <c r="Q21" t="s">
-        <v>32</v>
-      </c>
-      <c r="R21" t="s">
-        <v>32</v>
-      </c>
       <c r="S21" t="s">
         <v>32</v>
       </c>
       <c r="T21" t="s">
+        <v>32</v>
+      </c>
+      <c r="U21" t="s">
+        <v>32</v>
+      </c>
+      <c r="V21" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" t="s">
-        <v>164</v>
+        <v>32</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.0</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -4527,49 +4749,55 @@
       <c r="O22" t="s">
         <v>32</v>
       </c>
-      <c r="P22" t="b">
+      <c r="P22" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="b">
         <v>0</v>
       </c>
-      <c r="Q22" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" t="s">
-        <v>32</v>
-      </c>
       <c r="S22" t="s">
         <v>32</v>
       </c>
       <c r="T22" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C23" t="s">
         <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" t="s">
-        <v>167</v>
+        <v>32</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.0</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -4589,50 +4817,56 @@
       <c r="O23" t="s">
         <v>32</v>
       </c>
-      <c r="P23" t="b">
+      <c r="P23" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" t="b">
         <v>0</v>
       </c>
-      <c r="Q23" t="s">
-        <v>32</v>
-      </c>
-      <c r="R23" t="s">
-        <v>32</v>
-      </c>
       <c r="S23" t="s">
         <v>32</v>
       </c>
       <c r="T23" t="s">
+        <v>32</v>
+      </c>
+      <c r="U23" t="s">
+        <v>32</v>
+      </c>
+      <c r="V23" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" t="s">
         <v>107</v>
       </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" t="s">
-        <v>32</v>
-      </c>
       <c r="J24" t="s">
         <v>32</v>
       </c>
@@ -4651,49 +4885,55 @@
       <c r="O24" t="s">
         <v>32</v>
       </c>
-      <c r="P24" t="b">
-        <v>0</v>
+      <c r="P24" t="s">
+        <v>32</v>
       </c>
       <c r="Q24" t="s">
         <v>32</v>
       </c>
-      <c r="R24" t="s">
-        <v>32</v>
+      <c r="R24" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T24" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="U24" t="s">
+        <v>33</v>
+      </c>
+      <c r="V24" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
         <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" t="s">
-        <v>171</v>
+        <v>32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.0</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -4713,49 +4953,55 @@
       <c r="O25" t="s">
         <v>32</v>
       </c>
-      <c r="P25" s="3" t="b">
-        <v>1</v>
+      <c r="P25" t="s">
+        <v>32</v>
       </c>
       <c r="Q25" t="s">
-        <v>28</v>
-      </c>
-      <c r="R25" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T25" t="s">
-        <v>50</v>
+        <v>32</v>
+      </c>
+      <c r="U25" t="s">
+        <v>32</v>
+      </c>
+      <c r="V25" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C26" t="s">
         <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
-      </c>
-      <c r="G26" t="s">
-        <v>79</v>
+        <v>32</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.0</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -4775,49 +5021,55 @@
       <c r="O26" t="s">
         <v>32</v>
       </c>
-      <c r="P26" t="b">
+      <c r="P26" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" t="b">
         <v>0</v>
       </c>
-      <c r="Q26" t="s">
-        <v>32</v>
-      </c>
-      <c r="R26" t="s">
-        <v>32</v>
-      </c>
       <c r="S26" t="s">
         <v>32</v>
       </c>
       <c r="T26" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" t="s">
+        <v>32</v>
+      </c>
+      <c r="V26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
-      </c>
-      <c r="G27" t="s">
-        <v>80</v>
+        <v>180</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.0</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J27" t="s">
         <v>32</v>
@@ -4837,49 +5089,55 @@
       <c r="O27" t="s">
         <v>32</v>
       </c>
-      <c r="P27" t="b">
+      <c r="P27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" t="b">
         <v>0</v>
       </c>
-      <c r="Q27" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" t="s">
-        <v>32</v>
-      </c>
       <c r="S27" t="s">
         <v>32</v>
       </c>
       <c r="T27" t="s">
+        <v>32</v>
+      </c>
+      <c r="U27" t="s">
+        <v>32</v>
+      </c>
+      <c r="V27" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
         <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
-      </c>
-      <c r="G28" t="s">
-        <v>178</v>
+        <v>123</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.0</v>
       </c>
       <c r="H28" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="I28" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J28" t="s">
         <v>32</v>
@@ -4899,49 +5157,55 @@
       <c r="O28" t="s">
         <v>32</v>
       </c>
-      <c r="P28" t="b">
+      <c r="P28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" t="b">
         <v>0</v>
       </c>
-      <c r="Q28" t="s">
-        <v>32</v>
-      </c>
-      <c r="R28" t="s">
-        <v>32</v>
-      </c>
       <c r="S28" t="s">
         <v>32</v>
       </c>
       <c r="T28" t="s">
+        <v>32</v>
+      </c>
+      <c r="U28" t="s">
+        <v>32</v>
+      </c>
+      <c r="V28" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G29" t="s">
-        <v>83</v>
+        <v>32</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.0</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="I29" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J29" t="s">
         <v>32</v>
@@ -4961,49 +5225,55 @@
       <c r="O29" t="s">
         <v>32</v>
       </c>
-      <c r="P29" t="b">
+      <c r="P29" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" t="b">
         <v>0</v>
       </c>
-      <c r="Q29" t="s">
-        <v>32</v>
-      </c>
-      <c r="R29" t="s">
-        <v>32</v>
-      </c>
       <c r="S29" t="s">
         <v>32</v>
       </c>
       <c r="T29" t="s">
+        <v>32</v>
+      </c>
+      <c r="U29" t="s">
+        <v>32</v>
+      </c>
+      <c r="V29" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C30" t="s">
         <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" t="s">
-        <v>84</v>
+        <v>209</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.0</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J30" t="s">
         <v>32</v>
@@ -5023,49 +5293,55 @@
       <c r="O30" t="s">
         <v>32</v>
       </c>
-      <c r="P30" t="b">
+      <c r="P30" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" t="b">
         <v>0</v>
       </c>
-      <c r="Q30" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" t="s">
-        <v>32</v>
-      </c>
       <c r="S30" t="s">
         <v>32</v>
       </c>
       <c r="T30" t="s">
+        <v>32</v>
+      </c>
+      <c r="U30" t="s">
+        <v>32</v>
+      </c>
+      <c r="V30" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="B31" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" t="s">
-        <v>147</v>
+        <v>32</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.0</v>
       </c>
       <c r="H31" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="I31" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J31" t="s">
         <v>32</v>
@@ -5085,49 +5361,55 @@
       <c r="O31" t="s">
         <v>32</v>
       </c>
-      <c r="P31" t="b">
+      <c r="P31" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" t="b">
         <v>0</v>
       </c>
-      <c r="Q31" t="s">
-        <v>32</v>
-      </c>
-      <c r="R31" t="s">
-        <v>32</v>
-      </c>
       <c r="S31" t="s">
         <v>32</v>
       </c>
       <c r="T31" t="s">
+        <v>32</v>
+      </c>
+      <c r="U31" t="s">
+        <v>32</v>
+      </c>
+      <c r="V31" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="E32" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s">
-        <v>103</v>
-      </c>
-      <c r="G32" t="s">
-        <v>87</v>
+        <v>32</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.0</v>
       </c>
       <c r="H32" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="I32" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J32" t="s">
         <v>32</v>
@@ -5147,49 +5429,55 @@
       <c r="O32" t="s">
         <v>32</v>
       </c>
-      <c r="P32" t="b">
+      <c r="P32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" t="b">
         <v>0</v>
       </c>
-      <c r="Q32" t="s">
-        <v>32</v>
-      </c>
-      <c r="R32" t="s">
-        <v>32</v>
-      </c>
       <c r="S32" t="s">
         <v>32</v>
       </c>
       <c r="T32" t="s">
+        <v>32</v>
+      </c>
+      <c r="U32" t="s">
+        <v>32</v>
+      </c>
+      <c r="V32" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C33" t="s">
         <v>34</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
-        <v>103</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
+        <v>32</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.0</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J33" t="s">
         <v>32</v>
@@ -5209,49 +5497,55 @@
       <c r="O33" t="s">
         <v>32</v>
       </c>
-      <c r="P33" t="b">
+      <c r="P33" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" t="b">
         <v>0</v>
       </c>
-      <c r="Q33" t="s">
-        <v>32</v>
-      </c>
-      <c r="R33" t="s">
-        <v>32</v>
-      </c>
       <c r="S33" t="s">
         <v>32</v>
       </c>
       <c r="T33" t="s">
+        <v>32</v>
+      </c>
+      <c r="U33" t="s">
+        <v>32</v>
+      </c>
+      <c r="V33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="C34" t="s">
         <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
+        <v>32</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.0</v>
       </c>
       <c r="H34" t="s">
-        <v>32</v>
+        <v>161</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J34" t="s">
         <v>32</v>
@@ -5271,49 +5565,55 @@
       <c r="O34" t="s">
         <v>32</v>
       </c>
-      <c r="P34" t="b">
+      <c r="P34" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" t="b">
         <v>0</v>
       </c>
-      <c r="Q34" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" t="s">
-        <v>32</v>
-      </c>
       <c r="S34" t="s">
         <v>32</v>
       </c>
       <c r="T34" t="s">
+        <v>32</v>
+      </c>
+      <c r="U34" t="s">
+        <v>32</v>
+      </c>
+      <c r="V34" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C35" t="s">
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="F35" t="s">
-        <v>103</v>
-      </c>
-      <c r="G35" t="s">
-        <v>156</v>
+        <v>32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.0</v>
       </c>
       <c r="H35" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
         <v>32</v>
@@ -5333,50 +5633,56 @@
       <c r="O35" t="s">
         <v>32</v>
       </c>
-      <c r="P35" t="b">
+      <c r="P35" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" t="b">
         <v>0</v>
       </c>
-      <c r="Q35" t="s">
-        <v>32</v>
-      </c>
-      <c r="R35" t="s">
-        <v>32</v>
-      </c>
       <c r="S35" t="s">
         <v>32</v>
       </c>
       <c r="T35" t="s">
+        <v>32</v>
+      </c>
+      <c r="U35" t="s">
+        <v>32</v>
+      </c>
+      <c r="V35" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C36" t="s">
         <v>34</v>
       </c>
       <c r="D36" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>169</v>
+      </c>
+      <c r="I36" t="s">
         <v>107</v>
       </c>
-      <c r="E36" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" t="s">
-        <v>103</v>
-      </c>
-      <c r="G36" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" t="s">
-        <v>32</v>
-      </c>
       <c r="J36" t="s">
         <v>32</v>
       </c>
@@ -5395,49 +5701,55 @@
       <c r="O36" t="s">
         <v>32</v>
       </c>
-      <c r="P36" t="b">
+      <c r="P36" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" t="b">
         <v>0</v>
       </c>
-      <c r="Q36" t="s">
-        <v>32</v>
-      </c>
-      <c r="R36" t="s">
-        <v>32</v>
-      </c>
       <c r="S36" t="s">
         <v>32</v>
       </c>
       <c r="T36" t="s">
+        <v>32</v>
+      </c>
+      <c r="U36" t="s">
+        <v>32</v>
+      </c>
+      <c r="V36" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C37" t="s">
         <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="F37" t="s">
-        <v>103</v>
-      </c>
-      <c r="G37" t="s">
-        <v>70</v>
+        <v>32</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.0</v>
       </c>
       <c r="H37" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J37" t="s">
         <v>32</v>
@@ -5457,19 +5769,25 @@
       <c r="O37" t="s">
         <v>32</v>
       </c>
-      <c r="P37" t="b">
+      <c r="P37" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" t="b">
         <v>0</v>
       </c>
-      <c r="Q37" t="s">
-        <v>32</v>
-      </c>
-      <c r="R37" t="s">
-        <v>32</v>
-      </c>
       <c r="S37" t="s">
         <v>32</v>
       </c>
       <c r="T37" t="s">
+        <v>32</v>
+      </c>
+      <c r="U37" t="s">
+        <v>32</v>
+      </c>
+      <c r="V37" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5483,19 +5801,19 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="12.203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="12.140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5541,7 +5859,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -5582,44 +5900,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B3"/>
       <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
@@ -5636,19 +5932,19 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5694,7 +5990,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -5731,6 +6027,1102 @@
       </c>
       <c r="M2" s="1" t="s">
         <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView activeTab="2"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" r:id="rId3" sheetId="1"/>
@@ -11,15 +11,17 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Theme view" r:id="rId8" sheetId="6"/>
-    <sheet name="Sector view" r:id="rId9" sheetId="7"/>
-    <sheet name="Speaker view" r:id="rId10" sheetId="8"/>
+    <sheet name="Room view" r:id="rId8" sheetId="6"/>
+    <sheet name="Speaker view" r:id="rId9" sheetId="7"/>
+    <sheet name="Theme view" r:id="rId10" sheetId="8"/>
+    <sheet name="Sector view" r:id="rId11" sheetId="9"/>
+    <sheet name="Content view" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="233">
   <si>
     <t>Conference name</t>
   </si>
@@ -705,13 +707,19 @@
     <t>Chad Green, Dan Jones</t>
   </si>
   <si>
+    <t>Speaker</t>
+  </si>
+  <si>
     <t>Theme tag</t>
   </si>
   <si>
     <t>Sector tag</t>
   </si>
   <si>
-    <t>Speaker</t>
+    <t>Content tag</t>
+  </si>
+  <si>
+    <t>(2) S22</t>
   </si>
 </sst>
 </file>
@@ -943,6 +951,137 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.78515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -5801,6 +5940,1419 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" width="6.44921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
     <col min="1" max="1" width="12.140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -5859,7 +7411,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -5927,7 +7479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -5990,7 +7542,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -6027,1102 +7579,6 @@
       </c>
       <c r="M2" s="1" t="s">
         <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
-  <mergeCells>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-  </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" t="s">
-        <v>32</v>
-      </c>
-      <c r="M18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" t="s">
-        <v>32</v>
-      </c>
-      <c r="L20" t="s">
-        <v>32</v>
-      </c>
-      <c r="M20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" t="s">
-        <v>32</v>
-      </c>
-      <c r="M21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L22" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L24" t="s">
-        <v>32</v>
-      </c>
-      <c r="M24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
-        <v>32</v>
-      </c>
-      <c r="J25" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="235">
   <si>
     <t>Conference name</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>Soft penalty per common sector of 2 talks that have an overlapping timeslot</t>
+  </si>
+  <si>
+    <t>Content audience level flow violation</t>
+  </si>
+  <si>
+    <t>Soft penalty per common content of 2 talks with a different audience level for which the easier talk isn't scheduled earlier than the other talk.</t>
   </si>
   <si>
     <t>Language diversity</t>
@@ -795,14 +801,54 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.5" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="23.85546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="70.88671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="130.52734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -888,12 +934,12 @@
         <v>10.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="n">
         <v>10.0</v>
@@ -904,13 +950,13 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="n">
         <v>10.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -932,12 +978,12 @@
         <v>10.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="n">
         <v>10.0</v>
@@ -946,13 +992,25 @@
         <v>20</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -973,93 +1031,93 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1073,17 +1131,17 @@
       <c r="M3"/>
     </row>
   </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
   <mergeCells>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -1096,232 +1154,233 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -1343,310 +1402,310 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1655,11 +1714,12 @@
     <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -1688,1692 +1748,1692 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -3382,11 +3442,12 @@
     <mergeCell ref="P1:U1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -3416,2527 +3477,2528 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G3" t="n">
         <v>1.0</v>
       </c>
       <c r="H3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
       </c>
       <c r="H4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
         <v>3.0</v>
       </c>
       <c r="H5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>2.0</v>
       </c>
       <c r="H6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
       </c>
       <c r="H7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
         <v>2.0</v>
       </c>
       <c r="H9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
         <v>2.0</v>
       </c>
       <c r="H10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
       </c>
       <c r="H11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
         <v>3.0</v>
       </c>
       <c r="H12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
       </c>
       <c r="H13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
       </c>
       <c r="H14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
       </c>
       <c r="H15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
         <v>2.0</v>
       </c>
       <c r="H16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
         <v>1.0</v>
       </c>
       <c r="H17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
         <v>2.0</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G19" t="n">
         <v>2.0</v>
       </c>
       <c r="H19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G20" t="n">
         <v>2.0</v>
       </c>
       <c r="H20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
         <v>2.0</v>
       </c>
       <c r="H21" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E22" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
         <v>1.0</v>
       </c>
       <c r="H22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
         <v>2.0</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
         <v>2.0</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R24" s="3" t="b">
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="U24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="V24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B25" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
         <v>2.0</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" t="n">
         <v>3.0</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B27" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E27" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G27" t="n">
         <v>3.0</v>
       </c>
       <c r="H27" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I27" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
       </c>
       <c r="H29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G30" t="n">
         <v>3.0</v>
       </c>
       <c r="H30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B31" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
         <v>2.0</v>
       </c>
       <c r="H31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
         <v>3.0</v>
       </c>
       <c r="H32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G33" t="n">
         <v>2.0</v>
       </c>
       <c r="H33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G34" t="n">
         <v>3.0</v>
       </c>
       <c r="H34" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I34" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
       </c>
       <c r="H35" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
       </c>
       <c r="H36" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G37" t="n">
         <v>1.0</v>
       </c>
       <c r="H37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -5957,303 +6019,303 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
   <mergeCells>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -6274,1082 +6336,1082 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
   <mergeCells>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -7370,93 +7432,93 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -7470,17 +7532,17 @@
       <c r="M3"/>
     </row>
   </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
   <mergeCells>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -7501,92 +7563,92 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
   <mergeCells>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -11,11 +11,11 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Room view" r:id="rId8" sheetId="6"/>
-    <sheet name="Speaker view" r:id="rId9" sheetId="7"/>
-    <sheet name="Theme view" r:id="rId10" sheetId="8"/>
-    <sheet name="Sector view" r:id="rId11" sheetId="9"/>
-    <sheet name="Content view" r:id="rId12" sheetId="10"/>
+    <sheet name="Rooms view" r:id="rId8" sheetId="6"/>
+    <sheet name="Speakers view" r:id="rId9" sheetId="7"/>
+    <sheet name="Theme tracks view" r:id="rId10" sheetId="8"/>
+    <sheet name="Sectors view" r:id="rId11" sheetId="9"/>
+    <sheet name="Contents view" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
@@ -38,10 +38,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Theme conflict</t>
-  </si>
-  <si>
-    <t>Soft penalty per common theme of 2 talks that have an overlapping timeslot</t>
+    <t>Theme track conflict</t>
+  </si>
+  <si>
+    <t>Soft penalty per common theme track of 2 talks that have an overlapping timeslot</t>
   </si>
   <si>
     <t>Sector conflict</t>
@@ -185,420 +185,420 @@
     <t>Large, Recorded</t>
   </si>
   <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Theme track tags</t>
+  </si>
+  <si>
+    <t>Sector tags</t>
+  </si>
+  <si>
+    <t>Audience level</t>
+  </si>
+  <si>
+    <t>Content tags</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Pinned by user</t>
+  </si>
+  <si>
+    <t>Timeslot day</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>S00</t>
+  </si>
+  <si>
+    <t>Hands on real-time OpenShift</t>
+  </si>
+  <si>
+    <t>Amy Cole, Beth Fox</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>OpenShift</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>Lab_room</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Dan Jones, Elsa King</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Flo Li, Gus Poe</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Middleware, Cloud</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Cloud, Modern Web</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Culture, Mobile</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Ivy Watt, Jay Cole</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Security, Middleware</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Beth Fox, Chad Green</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
     <t>S22</t>
   </si>
   <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Speakers</t>
-  </si>
-  <si>
-    <t>Theme tags</t>
-  </si>
-  <si>
-    <t>Sector tags</t>
-  </si>
-  <si>
-    <t>Audience level</t>
-  </si>
-  <si>
-    <t>Content tags</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Pinned by user</t>
-  </si>
-  <si>
-    <t>Timeslot day</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>S00</t>
-  </si>
-  <si>
-    <t>Hands on real-time OpenShift</t>
-  </si>
-  <si>
-    <t>Amy Cole, Beth Fox</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>OpenShift</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Dan Jones, Elsa King</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Flo Li, Gus Poe</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Middleware, Cloud</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Cloud, Modern Web</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Culture, Mobile</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Ivy Watt, Jay Cole</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>Beth Jones, Chad King</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>Security, Middleware</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Beth Fox, Chad Green</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
     <t>Learn virtualized Drools</t>
   </si>
   <si>
@@ -716,7 +716,7 @@
     <t>Speaker</t>
   </si>
   <si>
-    <t>Theme tag</t>
+    <t>Theme track tag</t>
   </si>
   <si>
     <t>Sector tag</t>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
@@ -1498,8 +1498,8 @@
       <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>54</v>
+      <c r="D3" t="s">
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
         <v>56</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>34</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
@@ -1816,28 +1816,28 @@
         <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>46</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -2026,7 +2026,7 @@
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" t="s">
         <v>34</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -2168,7 +2168,7 @@
         <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
         <v>34</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -2286,7 +2286,7 @@
         <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
         <v>34</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -2481,7 +2481,7 @@
         <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -2983,7 +2983,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -3477,61 +3477,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>26</v>
@@ -3540,24 +3540,24 @@
         <v>27</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
         <v>104</v>
-      </c>
-      <c r="B2" t="s">
-        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" t="s">
         <v>106</v>
-      </c>
-      <c r="E2" t="s">
-        <v>107</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -3566,25 +3566,25 @@
         <v>3.0</v>
       </c>
       <c r="H2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" t="s">
         <v>108</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
         <v>109</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" t="s">
-        <v>110</v>
       </c>
       <c r="O2" t="s">
         <v>34</v>
@@ -3613,46 +3613,46 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
         <v>111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>112</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" t="s">
         <v>113</v>
-      </c>
-      <c r="F3" t="s">
-        <v>114</v>
       </c>
       <c r="G3" t="n">
         <v>1.0</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
         <v>109</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" t="s">
-        <v>110</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -3681,19 +3681,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
         <v>116</v>
-      </c>
-      <c r="B4" t="s">
-        <v>117</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" t="s">
         <v>118</v>
-      </c>
-      <c r="E4" t="s">
-        <v>119</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3702,25 +3702,25 @@
         <v>2.0</v>
       </c>
       <c r="H4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
         <v>109</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" t="s">
-        <v>110</v>
       </c>
       <c r="O4" t="s">
         <v>34</v>
@@ -3749,46 +3749,46 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
         <v>121</v>
-      </c>
-      <c r="B5" t="s">
-        <v>122</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" t="s">
         <v>123</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>124</v>
-      </c>
-      <c r="F5" t="s">
-        <v>125</v>
       </c>
       <c r="G5" t="n">
         <v>3.0</v>
       </c>
       <c r="H5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" t="s">
         <v>109</v>
-      </c>
-      <c r="J5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5" t="s">
-        <v>110</v>
       </c>
       <c r="O5" t="s">
         <v>34</v>
@@ -3817,19 +3817,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" t="s">
         <v>127</v>
-      </c>
-      <c r="B6" t="s">
-        <v>128</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -3838,10 +3838,10 @@
         <v>2.0</v>
       </c>
       <c r="H6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J6" t="s">
         <v>34</v>
@@ -3885,19 +3885,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
         <v>130</v>
-      </c>
-      <c r="B7" t="s">
-        <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -3906,10 +3906,10 @@
         <v>2.0</v>
       </c>
       <c r="H7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
         <v>34</v>
@@ -3953,19 +3953,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" t="s">
         <v>134</v>
-      </c>
-      <c r="B8" t="s">
-        <v>135</v>
       </c>
       <c r="C8" t="s">
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -3974,10 +3974,10 @@
         <v>1.0</v>
       </c>
       <c r="H8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J8" t="s">
         <v>34</v>
@@ -4021,19 +4021,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" t="s">
         <v>138</v>
-      </c>
-      <c r="B9" t="s">
-        <v>139</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -4042,10 +4042,10 @@
         <v>2.0</v>
       </c>
       <c r="H9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -4089,19 +4089,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" t="s">
         <v>141</v>
-      </c>
-      <c r="B10" t="s">
-        <v>142</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -4110,10 +4110,10 @@
         <v>2.0</v>
       </c>
       <c r="H10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J10" t="s">
         <v>34</v>
@@ -4157,19 +4157,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" t="s">
         <v>144</v>
-      </c>
-      <c r="B11" t="s">
-        <v>145</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -4178,10 +4178,10 @@
         <v>2.0</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -4225,19 +4225,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" t="s">
         <v>148</v>
-      </c>
-      <c r="B12" t="s">
-        <v>149</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
@@ -4246,10 +4246,10 @@
         <v>3.0</v>
       </c>
       <c r="H12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
         <v>34</v>
@@ -4293,19 +4293,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" t="s">
         <v>152</v>
-      </c>
-      <c r="B13" t="s">
-        <v>153</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -4314,10 +4314,10 @@
         <v>1.0</v>
       </c>
       <c r="H13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J13" t="s">
         <v>34</v>
@@ -4361,19 +4361,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" t="s">
         <v>156</v>
-      </c>
-      <c r="B14" t="s">
-        <v>157</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -4382,10 +4382,10 @@
         <v>3.0</v>
       </c>
       <c r="H14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J14" t="s">
         <v>34</v>
@@ -4429,19 +4429,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" t="s">
         <v>160</v>
-      </c>
-      <c r="B15" t="s">
-        <v>161</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -4450,10 +4450,10 @@
         <v>2.0</v>
       </c>
       <c r="H15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J15" t="s">
         <v>34</v>
@@ -4497,19 +4497,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s">
         <v>164</v>
-      </c>
-      <c r="B16" t="s">
-        <v>165</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F16" t="s">
         <v>34</v>
@@ -4518,10 +4518,10 @@
         <v>2.0</v>
       </c>
       <c r="H16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J16" t="s">
         <v>34</v>
@@ -4565,19 +4565,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" t="s">
         <v>167</v>
-      </c>
-      <c r="B17" t="s">
-        <v>168</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" t="s">
         <v>169</v>
-      </c>
-      <c r="E17" t="s">
-        <v>170</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -4586,10 +4586,10 @@
         <v>1.0</v>
       </c>
       <c r="H17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J17" t="s">
         <v>34</v>
@@ -4633,19 +4633,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" t="s">
         <v>172</v>
-      </c>
-      <c r="B18" t="s">
-        <v>173</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
@@ -4654,10 +4654,10 @@
         <v>2.0</v>
       </c>
       <c r="H18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J18" t="s">
         <v>34</v>
@@ -4701,31 +4701,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" t="s">
         <v>175</v>
-      </c>
-      <c r="B19" t="s">
-        <v>176</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G19" t="n">
         <v>2.0</v>
       </c>
       <c r="H19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J19" t="s">
         <v>34</v>
@@ -4769,31 +4769,31 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" t="s">
         <v>179</v>
-      </c>
-      <c r="B20" t="s">
-        <v>180</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" t="s">
         <v>181</v>
-      </c>
-      <c r="F20" t="s">
-        <v>182</v>
       </c>
       <c r="G20" t="n">
         <v>2.0</v>
       </c>
       <c r="H20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -4837,19 +4837,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" t="s">
         <v>184</v>
-      </c>
-      <c r="B21" t="s">
-        <v>185</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -4858,10 +4858,10 @@
         <v>2.0</v>
       </c>
       <c r="H21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J21" t="s">
         <v>34</v>
@@ -4905,19 +4905,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" t="s">
         <v>187</v>
-      </c>
-      <c r="B22" t="s">
-        <v>188</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
@@ -4926,10 +4926,10 @@
         <v>1.0</v>
       </c>
       <c r="H22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J22" t="s">
         <v>34</v>
@@ -4973,19 +4973,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" t="s">
         <v>190</v>
-      </c>
-      <c r="B23" t="s">
-        <v>191</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -4994,10 +4994,10 @@
         <v>2.0</v>
       </c>
       <c r="H23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J23" t="s">
         <v>34</v>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="B24" t="s">
         <v>192</v>
@@ -5050,10 +5050,10 @@
         <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
@@ -5062,10 +5062,10 @@
         <v>2.0</v>
       </c>
       <c r="H24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -5118,10 +5118,10 @@
         <v>36</v>
       </c>
       <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" t="s">
         <v>123</v>
-      </c>
-      <c r="E25" t="s">
-        <v>124</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -5130,10 +5130,10 @@
         <v>2.0</v>
       </c>
       <c r="H25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J25" t="s">
         <v>34</v>
@@ -5189,7 +5189,7 @@
         <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
@@ -5198,10 +5198,10 @@
         <v>3.0</v>
       </c>
       <c r="H26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J26" t="s">
         <v>34</v>
@@ -5260,16 +5260,16 @@
         <v>201</v>
       </c>
       <c r="F27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G27" t="n">
         <v>3.0</v>
       </c>
       <c r="H27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
         <v>34</v>
@@ -5328,16 +5328,16 @@
         <v>205</v>
       </c>
       <c r="F28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
         <v>34</v>
@@ -5390,7 +5390,7 @@
         <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
         <v>208</v>
@@ -5402,10 +5402,10 @@
         <v>3.0</v>
       </c>
       <c r="H29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -5458,10 +5458,10 @@
         <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" t="s">
         <v>211</v>
@@ -5470,10 +5470,10 @@
         <v>3.0</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J30" t="s">
         <v>34</v>
@@ -5526,10 +5526,10 @@
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -5538,10 +5538,10 @@
         <v>2.0</v>
       </c>
       <c r="H31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -5597,7 +5597,7 @@
         <v>216</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
@@ -5606,10 +5606,10 @@
         <v>3.0</v>
       </c>
       <c r="H32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J32" t="s">
         <v>34</v>
@@ -5665,7 +5665,7 @@
         <v>219</v>
       </c>
       <c r="E33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -5674,10 +5674,10 @@
         <v>2.0</v>
       </c>
       <c r="H33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J33" t="s">
         <v>34</v>
@@ -5730,10 +5730,10 @@
         <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F34" t="s">
         <v>34</v>
@@ -5742,10 +5742,10 @@
         <v>3.0</v>
       </c>
       <c r="H34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J34" t="s">
         <v>34</v>
@@ -5801,7 +5801,7 @@
         <v>224</v>
       </c>
       <c r="E35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5810,10 +5810,10 @@
         <v>1.0</v>
       </c>
       <c r="H35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J35" t="s">
         <v>34</v>
@@ -5866,10 +5866,10 @@
         <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
@@ -5878,10 +5878,10 @@
         <v>3.0</v>
       </c>
       <c r="H36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -5937,7 +5937,7 @@
         <v>229</v>
       </c>
       <c r="E37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
@@ -5946,10 +5946,10 @@
         <v>1.0</v>
       </c>
       <c r="H37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J37" t="s">
         <v>34</v>
@@ -6060,7 +6060,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>46</v>
@@ -6106,8 +6106,8 @@
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>54</v>
+      <c r="C3" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
@@ -6183,7 +6183,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>34</v>
@@ -6224,7 +6224,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>34</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -6459,7 +6459,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -6541,7 +6541,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -6582,13 +6582,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -6746,7 +6746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>34</v>
@@ -6787,7 +6787,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -6869,7 +6869,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -6910,7 +6910,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -7033,7 +7033,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -7197,7 +7197,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -7279,7 +7279,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -7361,7 +7361,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -7415,7 +7415,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.82421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -7514,11 +7514,11 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="237">
   <si>
     <t>Conference name</t>
   </si>
@@ -53,7 +53,13 @@
     <t>Content audience level flow violation</t>
   </si>
   <si>
-    <t>Soft penalty per common content of 2 talks with a different audience level for which the easier talk isn't scheduled earlier than the other talk.</t>
+    <t>Soft penalty per common content of 2 talks with a different audience level for which the easier talk isn't scheduled earlier than the other talk</t>
+  </si>
+  <si>
+    <t>Audience level diversity</t>
+  </si>
+  <si>
+    <t>Soft reward per 2 talks that have the same timeslot and a different audience level</t>
   </si>
   <si>
     <t>Language diversity</t>
@@ -848,7 +854,7 @@
   <cols>
     <col min="1" max="1" width="35.140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="23.85546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="130.52734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="129.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -909,7 +915,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -945,12 +951,12 @@
         <v>10.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>10.0</v>
@@ -961,13 +967,13 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>10.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -989,18 +995,29 @@
         <v>10.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="n">
         <v>10.0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1031,93 +1048,93 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1154,223 +1171,223 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1402,310 +1419,310 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1748,1692 +1765,1692 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3477,2518 +3494,2518 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
       </c>
       <c r="H2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
       </c>
       <c r="S2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G3" t="n">
         <v>1.0</v>
       </c>
       <c r="H3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
       </c>
       <c r="H4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G5" t="n">
         <v>3.0</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
         <v>2.0</v>
       </c>
       <c r="H6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
       </c>
       <c r="H7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
       </c>
       <c r="H8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
         <v>2.0</v>
       </c>
       <c r="H9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
         <v>2.0</v>
       </c>
       <c r="H10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
         <v>3.0</v>
       </c>
       <c r="H12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
       </c>
       <c r="H13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
       </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
       </c>
       <c r="H15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
         <v>2.0</v>
       </c>
       <c r="H16" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
         <v>1.0</v>
       </c>
       <c r="H17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
         <v>2.0</v>
       </c>
       <c r="H18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G19" t="n">
         <v>2.0</v>
       </c>
       <c r="H19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G20" t="n">
         <v>2.0</v>
       </c>
       <c r="H20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
         <v>2.0</v>
       </c>
       <c r="H21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
         <v>1.0</v>
       </c>
       <c r="H22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
         <v>2.0</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
         <v>2.0</v>
       </c>
       <c r="H24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R24" s="3" t="b">
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="U24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="V24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
         <v>2.0</v>
       </c>
       <c r="H25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B26" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
         <v>3.0</v>
       </c>
       <c r="H26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B27" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F27" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G27" t="n">
         <v>3.0</v>
       </c>
       <c r="H27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I27" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
       </c>
       <c r="H29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F30" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G30" t="n">
         <v>3.0</v>
       </c>
       <c r="H30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G31" t="n">
         <v>2.0</v>
       </c>
       <c r="H31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G32" t="n">
         <v>3.0</v>
       </c>
       <c r="H32" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G33" t="n">
         <v>2.0</v>
       </c>
       <c r="H33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
         <v>3.0</v>
       </c>
       <c r="H34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I34" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E35" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
       </c>
       <c r="H35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I35" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
       </c>
       <c r="H36" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I36" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G37" t="n">
         <v>1.0</v>
       </c>
       <c r="H37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -6019,289 +6036,289 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -6336,1068 +6353,1068 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -7432,93 +7449,93 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -7563,84 +7580,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -20,8 +20,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S22: Learn virtualized Drools
+  Elsa King
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S22: Learn virtualized Drools
+  Elsa King
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0">
+      <text>
+        <t>S22: Learn virtualized Drools
+  Elsa King
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S22: Learn virtualized Drools
+  Elsa King
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="238">
   <si>
     <t>Conference name</t>
   </si>
@@ -1047,6 +1115,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -1151,20 +1222,42 @@
       <c r="A3" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -1173,6 +1266,7 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -6035,6 +6129,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -6360,11 +6457,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -7456,11 +7557,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -7565,20 +7670,42 @@
       <c r="A3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -7587,11 +7714,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="261">
   <si>
     <t>Conference name</t>
   </si>
@@ -170,6 +170,75 @@
   </si>
   <si>
     <t>Talk undesired room tag</t>
+  </si>
+  <si>
+    <t>Talk type of timeslot</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Hard penalty per talk in a timeslot with an other talk type</t>
+  </si>
+  <si>
+    <t>Room unavailable timeslot</t>
+  </si>
+  <si>
+    <t>Hard penalty per talk with an unavailable room at its timeslot</t>
+  </si>
+  <si>
+    <t>Room conflict</t>
+  </si>
+  <si>
+    <t>Hard penalty per pair of talks in the same room in overlapping timeslots</t>
+  </si>
+  <si>
+    <t>Speaker unavailable timeslot</t>
+  </si>
+  <si>
+    <t>Hard penalty per talk with an unavailable speaker at its timeslot</t>
+  </si>
+  <si>
+    <t>Speaker conflict</t>
+  </si>
+  <si>
+    <t>Hard penalty per pair of talks with the same speaker in overlapping timeslots</t>
+  </si>
+  <si>
+    <t>Speaker required timeslot tag</t>
+  </si>
+  <si>
+    <t>Hard penalty per missing required tag in a talk's timeslot</t>
+  </si>
+  <si>
+    <t>Speaker prohibited timeslot tag</t>
+  </si>
+  <si>
+    <t>Hard penalty per prohibited tag in a talk's timeslot</t>
+  </si>
+  <si>
+    <t>Talk required timeslot tag</t>
+  </si>
+  <si>
+    <t>Talk prohibited timeslot tag</t>
+  </si>
+  <si>
+    <t>Speaker required room tag</t>
+  </si>
+  <si>
+    <t>Hard penalty per missing required tag in a talk's room</t>
+  </si>
+  <si>
+    <t>Speaker prohibited room tag</t>
+  </si>
+  <si>
+    <t>Hard penalty per prohibited tag in a talk's room</t>
+  </si>
+  <si>
+    <t>Talk required room tag</t>
+  </si>
+  <si>
+    <t>Talk prohibited room tag</t>
   </si>
   <si>
     <t>Day</t>
@@ -1107,6 +1176,150 @@
         <v>24</v>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
@@ -1138,125 +1351,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1284,223 +1497,223 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1532,310 +1745,310 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1878,1692 +2091,1692 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3607,2518 +3820,2518 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R24" s="4" t="b">
         <v>1</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="R37" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6165,289 +6378,289 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="30.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="30.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="30.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="30.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="30.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6486,1068 +6699,1068 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -7586,125 +7799,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -7743,84 +7956,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2175" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2175" uniqueCount="276">
   <si>
     <t>Conference name</t>
   </si>
@@ -316,202 +316,205 @@
     <t>End</t>
   </si>
   <si>
+    <t>Talk types</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>Mon 2018-10-01</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>Breakout</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>Tue 2018-10-02</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>10:15-12:15</t>
+  </si>
+  <si>
+    <t>10:15-11:00</t>
+  </si>
+  <si>
+    <t>11:30-12:15</t>
+  </si>
+  <si>
+    <t>13:00-15:00</t>
+  </si>
+  <si>
+    <t>15:30-16:15</t>
+  </si>
+  <si>
+    <t>16:30-17:15</t>
+  </si>
+  <si>
+    <t>R 1</t>
+  </si>
+  <si>
+    <t>Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>Talk type</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t>Mon 2018-10-01</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>Lab</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>Breakout</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>Tue 2018-10-02</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>10:15-12:15</t>
-  </si>
-  <si>
-    <t>10:15-11:00</t>
-  </si>
-  <si>
-    <t>11:30-12:15</t>
-  </si>
-  <si>
-    <t>13:00-15:00</t>
-  </si>
-  <si>
-    <t>15:30-16:15</t>
-  </si>
-  <si>
-    <t>16:30-17:15</t>
-  </si>
-  <si>
-    <t>R 1</t>
-  </si>
-  <si>
-    <t>Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
   </si>
   <si>
     <t>Speakers</t>
@@ -1524,7 +1527,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1565,13 +1568,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1681,7 +1684,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1722,13 +1725,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1838,7 +1841,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1879,13 +1882,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1937,7 +1940,7 @@
     <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="9.41796875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.29296875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="5.1484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4273,28 +4276,28 @@
         <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>91</v>
@@ -4321,10 +4324,10 @@
         <v>98</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -4333,39 +4336,39 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>65</v>
@@ -4380,7 +4383,7 @@
         <v>65</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>65</v>
@@ -4409,10 +4412,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
@@ -4421,22 +4424,22 @@
         <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
@@ -4451,7 +4454,7 @@
         <v>65</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>65</v>
@@ -4480,34 +4483,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
@@ -4522,7 +4525,7 @@
         <v>65</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>65</v>
@@ -4551,10 +4554,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
@@ -4563,22 +4566,22 @@
         <v>104</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
@@ -4593,7 +4596,7 @@
         <v>65</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>65</v>
@@ -4622,10 +4625,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>67</v>
@@ -4634,22 +4637,22 @@
         <v>105</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
@@ -4693,34 +4696,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>65</v>
@@ -4764,10 +4767,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>67</v>
@@ -4776,22 +4779,22 @@
         <v>108</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
@@ -4835,34 +4838,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
@@ -4906,34 +4909,34 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
@@ -4977,10 +4980,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>67</v>
@@ -4989,22 +4992,22 @@
         <v>113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
@@ -5048,10 +5051,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>67</v>
@@ -5060,22 +5063,22 @@
         <v>114</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>65</v>
@@ -5119,34 +5122,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>65</v>
@@ -5190,10 +5193,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>67</v>
@@ -5202,22 +5205,22 @@
         <v>117</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>65</v>
@@ -5261,10 +5264,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>67</v>
@@ -5273,22 +5276,22 @@
         <v>118</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>65</v>
@@ -5332,10 +5335,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>67</v>
@@ -5344,22 +5347,22 @@
         <v>119</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>65</v>
@@ -5403,10 +5406,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>67</v>
@@ -5415,22 +5418,22 @@
         <v>120</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -5474,10 +5477,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>67</v>
@@ -5486,22 +5489,22 @@
         <v>121</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -5545,10 +5548,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>67</v>
@@ -5557,22 +5560,22 @@
         <v>122</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>65</v>
@@ -5616,34 +5619,34 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>65</v>
@@ -5687,10 +5690,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>67</v>
@@ -5699,22 +5702,22 @@
         <v>101</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>65</v>
@@ -5758,34 +5761,34 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>65</v>
@@ -5829,10 +5832,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>67</v>
@@ -5841,22 +5844,22 @@
         <v>104</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>65</v>
@@ -5900,10 +5903,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>67</v>
@@ -5912,22 +5915,22 @@
         <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>65</v>
@@ -5971,10 +5974,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>67</v>
@@ -5983,22 +5986,22 @@
         <v>106</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>65</v>
@@ -6042,34 +6045,34 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>65</v>
@@ -6113,10 +6116,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>67</v>
@@ -6125,22 +6128,22 @@
         <v>109</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>65</v>
@@ -6184,34 +6187,34 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>65</v>
@@ -6255,10 +6258,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>67</v>
@@ -6267,22 +6270,22 @@
         <v>112</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>65</v>
@@ -6326,34 +6329,34 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>65</v>
@@ -6397,10 +6400,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>67</v>
@@ -6409,22 +6412,22 @@
         <v>115</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>65</v>
@@ -6468,10 +6471,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
@@ -6480,22 +6483,22 @@
         <v>116</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>65</v>
@@ -6539,34 +6542,34 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>65</v>
@@ -6610,34 +6613,34 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>65</v>
@@ -6681,34 +6684,34 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>65</v>
@@ -6752,10 +6755,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>67</v>
@@ -6764,22 +6767,22 @@
         <v>99</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>65</v>
@@ -6823,34 +6826,34 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>65</v>
@@ -6977,7 +6980,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -7024,7 +7027,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -7298,7 +7301,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -8165,7 +8168,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>65</v>
@@ -8398,7 +8401,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -8439,13 +8442,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -8555,7 +8558,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -11,34 +11,16 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Rooms view" r:id="rId8" sheetId="6"/>
-    <sheet name="Speakers view" r:id="rId9" sheetId="7"/>
-    <sheet name="Theme tracks view" r:id="rId10" sheetId="8"/>
-    <sheet name="Sectors view" r:id="rId11" sheetId="9"/>
-    <sheet name="Audience type view" r:id="rId12" sheetId="10"/>
-    <sheet name="Audience level view" r:id="rId13" sheetId="11"/>
-    <sheet name="Contents view" r:id="rId14" sheetId="12"/>
+    <sheet name="Score view" r:id="rId8" sheetId="6"/>
+    <sheet name="Rooms view" r:id="rId9" sheetId="7"/>
+    <sheet name="Speakers view" r:id="rId10" sheetId="8"/>
+    <sheet name="Theme tracks view" r:id="rId11" sheetId="9"/>
+    <sheet name="Sectors view" r:id="rId12" sheetId="10"/>
+    <sheet name="Audience type view" r:id="rId13" sheetId="11"/>
+    <sheet name="Audience level view" r:id="rId14" sheetId="12"/>
+    <sheet name="Contents view" r:id="rId15" sheetId="13"/>
   </sheets>
 </workbook>
-</file>
-
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0">
-      <text>
-        <t>S14: Troubleshooting reliable RestEasy
-  Amy Green
-  PINNED BY USER
-Constraint matches:
-  Speaker unavailable timeslot (S14): -1hard</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -79,7 +61,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
@@ -104,6 +86,25 @@
     <author/>
   </authors>
   <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S14: Troubleshooting reliable RestEasy
+  Amy Green
+  PINNED BY USER
+Constraint matches:
+  Speaker unavailable timeslot (S14): -1hard</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
     <comment ref="C23" authorId="0">
       <text>
         <t>S14: Troubleshooting reliable RestEasy
@@ -117,7 +118,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
@@ -137,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2175" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="280">
   <si>
     <t>Conference name</t>
   </si>
@@ -409,9 +410,6 @@
     <t>R 5</t>
   </si>
   <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
     <t>Required timeslot tags</t>
   </si>
   <si>
@@ -568,9 +566,6 @@
     <t>en</t>
   </si>
   <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
     <t>S01</t>
   </si>
   <si>
@@ -941,6 +936,24 @@
   </si>
   <si>
     <t>Beth Fox, Chad Green</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>-70init/-1hard</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Usable timeslots</t>
+  </si>
+  <si>
+    <t>Usable rooms</t>
+  </si>
+  <si>
+    <t>Usable sessions</t>
   </si>
   <si>
     <t>S14: Troubleshooting reliable RestEasy
@@ -1073,6 +1086,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
@@ -1469,6 +1486,121 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
     <col min="1" max="1" width="16.87890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -1527,7 +1659,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1568,13 +1700,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1618,7 +1750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -1684,7 +1816,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1725,13 +1857,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1775,7 +1907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -1841,7 +1973,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1882,13 +2014,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2177,8 +2309,8 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.48828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="25.6328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="10.29296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.51171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -2190,6 +2322,7 @@
     <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2200,11 +2333,11 @@
         <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>65</v>
       </c>
@@ -2218,11 +2351,11 @@
         <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="K1" s="1" t="s">
         <v>65</v>
       </c>
@@ -2233,6 +2366,9 @@
         <v>65</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2241,42 +2377,45 @@
         <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2285,42 +2424,45 @@
         <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="L3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2329,42 +2471,45 @@
         <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2373,42 +2518,45 @@
         <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="I5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M5" s="2" t="s">
+      <c r="L5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2417,42 +2565,45 @@
         <v>88</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="L6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2461,49 +2612,52 @@
         <v>89</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="I7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="L7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
@@ -2608,28 +2762,28 @@
         <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>77</v>
@@ -2670,7 +2824,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>65</v>
@@ -2735,7 +2889,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>65</v>
@@ -2800,7 +2954,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>65</v>
@@ -2865,7 +3019,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>65</v>
@@ -2930,7 +3084,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>65</v>
@@ -2995,7 +3149,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>65</v>
@@ -3060,7 +3214,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -3125,7 +3279,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -3190,7 +3344,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>65</v>
@@ -3255,7 +3409,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>65</v>
@@ -3320,7 +3474,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>65</v>
@@ -3385,7 +3539,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>65</v>
@@ -3450,7 +3604,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>65</v>
@@ -3515,7 +3669,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>65</v>
@@ -3580,7 +3734,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>65</v>
@@ -3645,7 +3799,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>65</v>
@@ -3710,7 +3864,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>65</v>
@@ -3775,7 +3929,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>65</v>
@@ -3840,7 +3994,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>65</v>
@@ -3905,7 +4059,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>65</v>
@@ -3970,7 +4124,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>65</v>
@@ -4035,7 +4189,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>65</v>
@@ -4100,7 +4254,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>65</v>
@@ -4165,7 +4319,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -4270,64 +4424,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -4336,40 +4490,40 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="K2" s="2" t="s">
         <v>65</v>
       </c>
@@ -4383,7 +4537,7 @@
         <v>65</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>65</v>
@@ -4412,34 +4566,34 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
@@ -4454,7 +4608,7 @@
         <v>65</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>65</v>
@@ -4483,34 +4637,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
@@ -4525,7 +4679,7 @@
         <v>65</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>65</v>
@@ -4554,34 +4708,34 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
@@ -4596,7 +4750,7 @@
         <v>65</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>65</v>
@@ -4625,34 +4779,34 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
@@ -4696,34 +4850,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>65</v>
@@ -4767,34 +4921,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
@@ -4838,34 +4992,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
@@ -4909,34 +5063,34 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
@@ -4980,34 +5134,34 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
@@ -5051,34 +5205,34 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>65</v>
@@ -5122,34 +5276,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>65</v>
@@ -5193,34 +5347,34 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>65</v>
@@ -5264,34 +5418,34 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>65</v>
@@ -5335,34 +5489,34 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>65</v>
@@ -5406,34 +5560,34 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -5477,34 +5631,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -5548,34 +5702,34 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>65</v>
@@ -5619,34 +5773,34 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>65</v>
@@ -5690,34 +5844,34 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>65</v>
@@ -5761,34 +5915,34 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>65</v>
@@ -5832,34 +5986,34 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>65</v>
@@ -5903,34 +6057,34 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>65</v>
@@ -5974,34 +6128,34 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>65</v>
@@ -6045,34 +6199,34 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>65</v>
@@ -6116,34 +6270,34 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>65</v>
@@ -6187,34 +6341,34 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>65</v>
@@ -6258,34 +6412,34 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>65</v>
@@ -6329,34 +6483,34 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>65</v>
@@ -6400,34 +6554,34 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>65</v>
@@ -6471,34 +6625,34 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>65</v>
@@ -6542,34 +6696,34 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>65</v>
@@ -6613,34 +6767,34 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>65</v>
@@ -6684,34 +6838,34 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>65</v>
@@ -6755,34 +6909,34 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>65</v>
@@ -6826,34 +6980,34 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>65</v>
@@ -6902,6 +7056,87 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="9.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.61328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.22265625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.59375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="15.30078125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>32.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -6980,7 +7215,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -7027,7 +7262,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -7235,7 +7470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -7301,7 +7536,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -7342,7 +7577,7 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
@@ -7383,7 +7618,7 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>65</v>
@@ -7424,7 +7659,7 @@
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>65</v>
@@ -7465,7 +7700,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>65</v>
@@ -7506,7 +7741,7 @@
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>65</v>
@@ -7547,7 +7782,7 @@
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>65</v>
@@ -7588,7 +7823,7 @@
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>65</v>
@@ -7629,7 +7864,7 @@
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>65</v>
@@ -7670,7 +7905,7 @@
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>65</v>
@@ -7711,7 +7946,7 @@
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>65</v>
@@ -7752,7 +7987,7 @@
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>65</v>
@@ -7793,7 +8028,7 @@
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>65</v>
@@ -7834,7 +8069,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>65</v>
@@ -7875,7 +8110,7 @@
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>65</v>
@@ -7916,7 +8151,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>65</v>
@@ -7957,7 +8192,7 @@
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>65</v>
@@ -7998,7 +8233,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>65</v>
@@ -8039,7 +8274,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>65</v>
@@ -8080,7 +8315,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>65</v>
@@ -8121,7 +8356,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>65</v>
@@ -8162,13 +8397,13 @@
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>65</v>
@@ -8203,7 +8438,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>65</v>
@@ -8244,7 +8479,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>65</v>
@@ -8285,7 +8520,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>65</v>
@@ -8335,7 +8570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -8401,7 +8636,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -8442,13 +8677,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -8490,119 +8725,4 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor rgb="FCE94F"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-  </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="282">
   <si>
     <t>Conference name</t>
   </si>
@@ -524,7 +524,7 @@
     <t>Sector tags</t>
   </si>
   <si>
-    <t>Audience type</t>
+    <t>Audience types</t>
   </si>
   <si>
     <t>Audience level</t>
@@ -954,6 +954,9 @@
   </si>
   <si>
     <t>Usable sessions</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>S14: Troubleshooting reliable RestEasy
@@ -970,6 +973,9 @@
   </si>
   <si>
     <t>Sector tag</t>
+  </si>
+  <si>
+    <t>Audience type</t>
   </si>
   <si>
     <t>2</t>
@@ -1544,7 +1550,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1659,7 +1665,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>278</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1706,7 +1712,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1857,13 +1863,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1973,7 +1979,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2020,7 +2026,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -7128,6 +7134,24 @@
       </c>
       <c r="E5" s="2" t="n">
         <v>32.0</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>60.0</v>
       </c>
     </row>
   </sheetData>
@@ -7262,7 +7286,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -7536,7 +7560,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -8403,7 +8427,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>65</v>
@@ -8636,7 +8660,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -8683,7 +8707,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -2435,7 +2435,7 @@
       <c r="C3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -2444,7 +2444,7 @@
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -2453,7 +2453,7 @@
       <c r="I3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -2462,7 +2462,7 @@
       <c r="L3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -2482,7 +2482,7 @@
       <c r="C4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -2491,7 +2491,7 @@
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -2500,7 +2500,7 @@
       <c r="I4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -2509,7 +2509,7 @@
       <c r="L4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N4" s="2" t="s">
@@ -2529,7 +2529,7 @@
       <c r="C5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -2538,7 +2538,7 @@
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -2547,7 +2547,7 @@
       <c r="I5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -2556,7 +2556,7 @@
       <c r="L5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
@@ -2576,7 +2576,7 @@
       <c r="C6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -2585,7 +2585,7 @@
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -2594,7 +2594,7 @@
       <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -2603,7 +2603,7 @@
       <c r="L6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -2626,37 +2626,37 @@
       <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="H7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="K7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O7" s="3" t="s">
+      <c r="N7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -1185,7 +1185,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -1207,7 +1207,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -1229,7 +1229,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -1251,7 +1251,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
@@ -1262,7 +1262,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
@@ -1273,7 +1273,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>22</v>
@@ -1284,7 +1284,7 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
@@ -1295,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -1306,7 +1306,7 @@
         <v>29</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -1317,7 +1317,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -1328,7 +1328,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -11,14 +11,16 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Score view" r:id="rId8" sheetId="6"/>
+    <sheet name="Infeasible view" r:id="rId8" sheetId="6"/>
     <sheet name="Rooms view" r:id="rId9" sheetId="7"/>
     <sheet name="Speakers view" r:id="rId10" sheetId="8"/>
     <sheet name="Theme tracks view" r:id="rId11" sheetId="9"/>
     <sheet name="Sectors view" r:id="rId12" sheetId="10"/>
-    <sheet name="Audience type view" r:id="rId13" sheetId="11"/>
-    <sheet name="Audience level view" r:id="rId14" sheetId="12"/>
+    <sheet name="Audience types view" r:id="rId13" sheetId="11"/>
+    <sheet name="Audience levels view" r:id="rId14" sheetId="12"/>
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
+    <sheet name="Languages view" r:id="rId16" sheetId="14"/>
+    <sheet name="Score view" r:id="rId17" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -31,11 +33,12 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S14: Troubleshooting reliable RestEasy
-  Amy Green
-  PINNED BY USER
-Constraint matches:
-  Speaker unavailable timeslot (S14): -1hard</t>
+        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
+    Amy Green
+PINNED BY USER
+-1hard total
+    -1hard for 1 Speaker unavailable timeslots
+</t>
       </text>
     </comment>
   </commentList>
@@ -50,11 +53,12 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S14: Troubleshooting reliable RestEasy
-  Amy Green
-  PINNED BY USER
-Constraint matches:
-  Speaker unavailable timeslot (S14): -1hard</t>
+        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
+    Amy Green
+PINNED BY USER
+-1hard total
+    -1hard for 1 Speaker unavailable timeslots
+</t>
       </text>
     </comment>
   </commentList>
@@ -69,11 +73,32 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S14: Troubleshooting reliable RestEasy
-  Amy Green
-  PINNED BY USER
-Constraint matches:
-  Speaker unavailable timeslot (S14): -1hard</t>
+        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
+    Amy Green
+PINNED BY USER
+-1hard total
+    -1hard for 1 Speaker unavailable timeslots
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
+    Amy Green
+PINNED BY USER
+-1hard total
+    -1hard for 1 Speaker unavailable timeslots
+</t>
       </text>
     </comment>
   </commentList>
@@ -88,11 +113,12 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S14: Troubleshooting reliable RestEasy
-  Amy Green
-  PINNED BY USER
-Constraint matches:
-  Speaker unavailable timeslot (S14): -1hard</t>
+        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
+    Amy Green
+PINNED BY USER
+-1hard total
+    -1hard for 1 Speaker unavailable timeslots
+</t>
       </text>
     </comment>
   </commentList>
@@ -107,11 +133,12 @@
   <commentList>
     <comment ref="C23" authorId="0">
       <text>
-        <t>S14: Troubleshooting reliable RestEasy
-  Amy Green
-  PINNED BY USER
-Constraint matches:
-  Speaker unavailable timeslot (S14): -1hard</t>
+        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
+    Amy Green
+PINNED BY USER
+-1hard total
+    -1hard for 1 Speaker unavailable timeslots
+</t>
       </text>
     </comment>
   </commentList>
@@ -126,11 +153,12 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S14: Troubleshooting reliable RestEasy
-  Amy Green
-  PINNED BY USER
-Constraint matches:
-  Speaker unavailable timeslot (S14): -1hard</t>
+        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
+    Amy Green
+PINNED BY USER
+-1hard total
+    -1hard for 1 Speaker unavailable timeslots
+</t>
       </text>
     </comment>
   </commentList>
@@ -138,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="287">
   <si>
     <t>Conference name</t>
   </si>
@@ -985,6 +1013,21 @@
   </si>
   <si>
     <t>S14 (level 2)</t>
+  </si>
+  <si>
+    <t>Constraint match</t>
+  </si>
+  <si>
+    <t>Match score</t>
+  </si>
+  <si>
+    <t>Total score</t>
+  </si>
+  <si>
+    <t>-1hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    S14</t>
   </si>
 </sst>
 </file>
@@ -1096,6 +1139,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
@@ -2070,6 +2121,219 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="true">
+      <c r="A3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="27.54296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="12.296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.08203125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
@@ -7151,7 +7415,7 @@
         <v>5.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60.0</v>
+        <v>36.0</v>
       </c>
     </row>
   </sheetData>
@@ -7278,7 +7542,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" ht="60.0" customHeight="true">
+    <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
         <v>83</v>
       </c>
@@ -7319,7 +7583,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" ht="60.0" customHeight="true">
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
@@ -7360,7 +7624,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" ht="60.0" customHeight="true">
+    <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
         <v>86</v>
       </c>
@@ -7401,7 +7665,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" ht="60.0" customHeight="true">
+    <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
         <v>88</v>
       </c>
@@ -7442,7 +7706,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" ht="60.0" customHeight="true">
+    <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
         <v>89</v>
       </c>
@@ -7503,18 +7767,31 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="20.0" customWidth="true"/>
+    <col min="3" max="3" width="20.0" customWidth="true"/>
+    <col min="4" max="4" width="20.0" customWidth="true"/>
+    <col min="5" max="5" width="20.0" customWidth="true"/>
+    <col min="6" max="6" width="20.0" customWidth="true"/>
+    <col min="7" max="7" width="20.0" customWidth="true"/>
+    <col min="8" max="8" width="20.0" customWidth="true"/>
+    <col min="9" max="9" width="20.0" customWidth="true"/>
+    <col min="10" max="10" width="20.0" customWidth="true"/>
+    <col min="11" max="11" width="20.0" customWidth="true"/>
+    <col min="12" max="12" width="20.0" customWidth="true"/>
+    <col min="13" max="13" width="20.0" customWidth="true"/>
+    <col min="14" max="14" width="20.0" customWidth="true"/>
+    <col min="15" max="15" width="20.0" customWidth="true"/>
+    <col min="16" max="16" width="20.0" customWidth="true"/>
+    <col min="17" max="17" width="20.0" customWidth="true"/>
+    <col min="18" max="18" width="20.0" customWidth="true"/>
+    <col min="19" max="19" width="20.0" customWidth="true"/>
+    <col min="20" max="20" width="20.0" customWidth="true"/>
+    <col min="21" max="21" width="20.0" customWidth="true"/>
+    <col min="22" max="22" width="20.0" customWidth="true"/>
+    <col min="23" max="23" width="20.0" customWidth="true"/>
+    <col min="24" max="24" width="20.0" customWidth="true"/>
+    <col min="25" max="25" width="20.0" customWidth="true"/>
+    <col min="26" max="26" width="20.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="296">
   <si>
     <t>Conference name</t>
   </si>
@@ -267,6 +267,12 @@
     <t>Talk undesired room tag</t>
   </si>
   <si>
+    <t>Same day talks</t>
+  </si>
+  <si>
+    <t>Soft penalty per common content/theme of 2 talks that are scheduled on different days</t>
+  </si>
+  <si>
     <t>Talk type of timeslot</t>
   </si>
   <si>
@@ -339,6 +345,18 @@
     <t>Talk prohibited room tag</t>
   </si>
   <si>
+    <t>Talk mutually-exclusive-talks tag</t>
+  </si>
+  <si>
+    <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
+  </si>
+  <si>
+    <t>Talk prerequisite talks</t>
+  </si>
+  <si>
+    <t>Hard penalty per talk that is scheduled before any of its prerequisite talks</t>
+  </si>
+  <si>
     <t>Day</t>
   </si>
   <si>
@@ -565,6 +583,12 @@
   </si>
   <si>
     <t>Language</t>
+  </si>
+  <si>
+    <t>Mutually exclusive talks tags</t>
+  </si>
+  <si>
+    <t>Prerequisite talks codes</t>
   </si>
   <si>
     <t>Pinned by user</t>
@@ -1396,18 +1420,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+    <row r="20">
+      <c r="A20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="B20" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="1" t="s">
         <v>35</v>
@@ -1435,7 +1459,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>40</v>
@@ -1446,7 +1470,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>42</v>
@@ -1493,12 +1517,12 @@
         <v>1.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1.0</v>
@@ -1509,13 +1533,13 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -1537,18 +1561,51 @@
         <v>1.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1582,84 +1639,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1697,125 +1754,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1854,125 +1911,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2011,125 +2068,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2168,131 +2225,131 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -2322,30 +2379,30 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2370,223 +2427,223 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2619,331 +2676,331 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2986,1692 +3043,1692 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -4707,2638 +4764,2862 @@
     <col min="16" max="16" width="22.20703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="23.125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="22.84375" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="16.65234375" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="16.14453125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="7.02734375" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="31.2734375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="26.23046875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="16.65234375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.14453125" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="6.3984375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="6.32421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="7.02734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>135</v>
+        <v>64</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S2" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S3" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S4" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S7" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S8" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S9" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S10" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S11" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S12" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S13" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U13" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S14" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S15" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S16" s="4" t="b">
+        <v>72</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="V16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S17" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U17" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S18" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U18" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S19" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S20" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U20" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S21" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U21" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S22" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U22" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S23" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U23" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S24" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U24" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S25" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U25" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S26" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U26" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S27" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S28" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S29" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S30" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S31" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S32" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T32" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S33" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S34" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U34" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S35" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S36" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U36" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T36" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S37" s="2" t="b">
+        <v>72</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U37" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T37" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U37" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -7364,33 +7645,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>4.0</v>
@@ -7407,7 +7688,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>32.0</v>
@@ -7425,7 +7706,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.0</v>
@@ -7484,289 +7765,289 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -7818,1068 +8099,1068 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -8918,125 +9199,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -25,6 +25,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
+PINNED BY USER
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -33,11 +51,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
-    Amy Green
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
 PINNED BY USER
--1hard total
-    -1hard for 1 Speaker unavailable timeslots
 </t>
       </text>
     </comment>
@@ -53,11 +69,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
-    Amy Green
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
 PINNED BY USER
--1hard total
-    -1hard for 1 Speaker unavailable timeslots
 </t>
       </text>
     </comment>
@@ -73,11 +87,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
-    Amy Green
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
 PINNED BY USER
--1hard total
-    -1hard for 1 Speaker unavailable timeslots
 </t>
       </text>
     </comment>
@@ -93,11 +105,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
-    Amy Green
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
 PINNED BY USER
--1hard total
-    -1hard for 1 Speaker unavailable timeslots
 </t>
       </text>
     </comment>
@@ -113,11 +123,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
-    Amy Green
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
 PINNED BY USER
--1hard total
-    -1hard for 1 Speaker unavailable timeslots
 </t>
       </text>
     </comment>
@@ -131,13 +139,11 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C23" authorId="0">
+    <comment ref="C18" authorId="0">
       <text>
-        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
-    Amy Green
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
 PINNED BY USER
--1hard total
-    -1hard for 1 Speaker unavailable timeslots
 </t>
       </text>
     </comment>
@@ -153,11 +159,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S14: Troubleshooting reliable RestEasy
-    Amy Green
+        <t xml:space="preserve">S31: Understand mobile Angular
+    Flo Poe
 PINNED BY USER
--1hard total
-    -1hard for 1 Speaker unavailable timeslots
 </t>
       </text>
     </comment>
@@ -166,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="289">
   <si>
     <t>Conference name</t>
   </si>
@@ -591,6 +595,12 @@
     <t>Prerequisite talks codes</t>
   </si>
   <si>
+    <t>Number of likes</t>
+  </si>
+  <si>
+    <t>Crowd control risk</t>
+  </si>
+  <si>
     <t>Pinned by user</t>
   </si>
   <si>
@@ -627,301 +637,298 @@
     <t>Advanced containerized WildFly</t>
   </si>
   <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Programmers</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Dan Jones, Elsa King</t>
+  </si>
+  <si>
+    <t>Modern Web, IoT</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Business analysts</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Gus Poe, Hugo Rye</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Cloud, Big Data</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye, Hugo Smith</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
     <t>Middleware</t>
   </si>
   <si>
-    <t>Programmers</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Dan Jones, Elsa King</t>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>Middleware, IoT</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Big Data, Cloud</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Modern Web, Big Data</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Beth Fox, Chad Green</t>
   </si>
   <si>
     <t>Culture</t>
   </si>
   <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Hugo Rye, Ivy Smith</t>
-  </si>
-  <si>
-    <t>Cloud, Big Data</t>
-  </si>
-  <si>
-    <t>Business analysts</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
   </si>
   <si>
     <t>Amy Fox, Beth Green</t>
   </si>
   <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Chad Jones, Dan King</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Docker, Kubernetes</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Middleware, Cloud</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Culture, Mobile</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Gus Rye, Hugo Smith</t>
-  </si>
-  <si>
-    <t>IoT, Modern Web</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Modern Web, Culture</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Culture</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>Culture, Security</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>Ivy Smith, Jay Watt</t>
-  </si>
-  <si>
     <t>Transportation</t>
   </si>
   <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Beth Green, Chad Jones</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
+    <t>Docker</t>
   </si>
   <si>
     <t>S28</t>
@@ -930,9 +937,6 @@
     <t>Securing scalable Hibernate</t>
   </si>
   <si>
-    <t>Elsa Li, Flo Poe</t>
-  </si>
-  <si>
     <t>S29</t>
   </si>
   <si>
@@ -951,28 +955,19 @@
     <t>Understand mobile Angular</t>
   </si>
   <si>
-    <t>Ivy Watt, Jay Cole</t>
-  </si>
-  <si>
     <t>S32</t>
   </si>
   <si>
     <t>Applying modern Weld</t>
   </si>
   <si>
-    <t>Amy Green, Beth Jones</t>
-  </si>
-  <si>
     <t>S33</t>
   </si>
   <si>
     <t>Grok distributed RestEasy</t>
   </si>
   <si>
-    <t>Chad King, Dan Li</t>
-  </si>
-  <si>
-    <t>Security, Culture</t>
+    <t>Hugo Smith, Ivy Watt</t>
   </si>
   <si>
     <t>S34</t>
@@ -981,22 +976,16 @@
     <t>Troubleshooting reliable Android</t>
   </si>
   <si>
-    <t>Mobile, Cloud</t>
-  </si>
-  <si>
     <t>S35</t>
   </si>
   <si>
     <t>Using secure Tensorflow</t>
   </si>
   <si>
-    <t>Beth Fox, Chad Green</t>
-  </si>
-  <si>
     <t>Score</t>
   </si>
   <si>
-    <t>-70init/-1hard</t>
+    <t>-70init</t>
   </si>
   <si>
     <t>Count</t>
@@ -1014,14 +1003,14 @@
     <t>Total</t>
   </si>
   <si>
-    <t>S14: Troubleshooting reliable RestEasy
-  Amy Green</t>
+    <t>S31: Understand mobile Angular
+  Flo Poe</t>
   </si>
   <si>
     <t>Speaker</t>
   </si>
   <si>
-    <t>S14 @ R 1</t>
+    <t>S31 @ R 1</t>
   </si>
   <si>
     <t>Theme track tag</t>
@@ -1039,7 +1028,7 @@
     <t>Content tag</t>
   </si>
   <si>
-    <t>S14 (level 2)</t>
+    <t>S31 (level 2)</t>
   </si>
   <si>
     <t>Constraint match</t>
@@ -1049,12 +1038,6 @@
   </si>
   <si>
     <t>Total score</t>
-  </si>
-  <si>
-    <t>-1hard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    S14</t>
   </si>
 </sst>
 </file>
@@ -1622,7 +1605,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="22.44140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
@@ -1680,7 +1663,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -1717,6 +1700,47 @@
       </c>
       <c r="M2" s="1" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="true">
+      <c r="A3" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1726,6 +1750,7 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1737,7 +1762,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
@@ -1795,7 +1820,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -1836,13 +1861,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -1993,13 +2018,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2109,7 +2134,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -2150,13 +2175,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2307,13 +2332,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2346,10 +2371,10 @@
         <v>72</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -2371,7 +2396,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="31.4140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.0703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.73828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true"/>
   </cols>
@@ -2379,33 +2404,14 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+        <v>288</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -4749,9 +4755,9 @@
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.3125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="22.8671875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="27.7109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.30859375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="28.3515625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="21.6953125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="20.05859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.34375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.3046875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="21.8046875" customWidth="true" bestFit="true"/>
@@ -4766,11 +4772,13 @@
     <col min="18" max="18" width="22.84375" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="31.2734375" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="26.23046875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="16.65234375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.14453125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="7.02734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="17.5390625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="20.140625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.65234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.14453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="6.3984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="6.32421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="7.02734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4841,45 +4849,51 @@
         <v>142</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>143</v>
+      <c r="AA1" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>72</v>
@@ -4911,28 +4925,34 @@
       <c r="T2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U2" s="2" t="b">
+      <c r="U2" s="2" t="n">
+        <v>639.0</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>71</v>
@@ -4941,99 +4961,105 @@
         <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>357.0</v>
+      </c>
+      <c r="V3" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U3" s="2" t="b">
+      <c r="W3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>72</v>
@@ -5065,28 +5091,34 @@
       <c r="T4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U4" s="2" t="b">
+      <c r="U4" s="2" t="n">
+        <v>945.0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X4" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>71</v>
@@ -5095,22 +5127,22 @@
         <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>72</v>
@@ -5142,52 +5174,58 @@
       <c r="T5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U5" s="2" t="b">
+      <c r="U5" s="2" t="n">
+        <v>325.0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X5" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA5" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>72</v>
@@ -5219,105 +5257,117 @@
       <c r="T6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U6" s="2" t="b">
+      <c r="U6" s="2" t="n">
+        <v>724.0</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X6" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="H7" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>259.0</v>
+      </c>
+      <c r="V7" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U7" s="2" t="b">
+      <c r="W7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA7" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>74</v>
@@ -5326,22 +5376,22 @@
         <v>114</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>72</v>
@@ -5373,52 +5423,58 @@
       <c r="T8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U8" s="2" t="b">
+      <c r="U8" s="2" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X8" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>182</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>72</v>
@@ -5450,19 +5506,25 @@
       <c r="T9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U9" s="2" t="b">
+      <c r="U9" s="2" t="n">
+        <v>558.0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5477,25 +5539,25 @@
         <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>72</v>
@@ -5527,52 +5589,58 @@
       <c r="T10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U10" s="2" t="b">
+      <c r="U10" s="2" t="n">
+        <v>264.0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA10" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>72</v>
@@ -5604,52 +5672,58 @@
       <c r="T11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U11" s="2" t="b">
+      <c r="U11" s="2" t="n">
+        <v>144.0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA11" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>72</v>
@@ -5681,52 +5755,58 @@
       <c r="T12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U12" s="2" t="b">
+      <c r="U12" s="2" t="n">
+        <v>840.0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X12" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA12" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>72</v>
@@ -5758,206 +5838,224 @@
       <c r="T13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U13" s="2" t="b">
+      <c r="U13" s="2" t="n">
+        <v>201.0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W13" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X13" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA13" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H14" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>543.0</v>
+      </c>
+      <c r="V14" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U14" s="2" t="b">
+      <c r="W14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X14" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA14" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H15" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>973.0</v>
+      </c>
+      <c r="V15" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U15" s="2" t="b">
+      <c r="W15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X15" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA15" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>72</v>
@@ -5989,52 +6087,58 @@
       <c r="T16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>69</v>
+      <c r="U16" s="2" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W16" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>72</v>
@@ -6066,105 +6170,117 @@
       <c r="T17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U17" s="2" t="b">
+      <c r="U17" s="2" t="n">
+        <v>871.0</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W17" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X17" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA17" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H18" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>411.0</v>
+      </c>
+      <c r="V18" s="2" t="n">
         <v>3.0</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U18" s="2" t="b">
+      <c r="W18" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA18" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>74</v>
@@ -6173,22 +6289,22 @@
         <v>128</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>72</v>
@@ -6220,52 +6336,58 @@
       <c r="T19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U19" s="2" t="b">
+      <c r="U19" s="2" t="n">
+        <v>118.0</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X19" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA19" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>72</v>
@@ -6297,52 +6419,58 @@
       <c r="T20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U20" s="2" t="b">
+      <c r="U20" s="2" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W20" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA20" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>107</v>
+        <v>227</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>72</v>
+        <v>229</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>72</v>
@@ -6374,52 +6502,58 @@
       <c r="T21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U21" s="2" t="b">
+      <c r="U21" s="2" t="n">
+        <v>142.0</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W21" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X21" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA21" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>72</v>
@@ -6451,129 +6585,141 @@
       <c r="T22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U22" s="2" t="b">
+      <c r="U22" s="2" t="n">
+        <v>287.0</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W22" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X22" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA22" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>72</v>
+        <v>235</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="H23" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>435.0</v>
+      </c>
+      <c r="V23" s="2" t="n">
         <v>3.0</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U23" s="2" t="b">
+      <c r="W23" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA23" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>237</v>
+        <v>72</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>72</v>
@@ -6605,19 +6751,25 @@
       <c r="T24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U24" s="2" t="b">
+      <c r="U24" s="2" t="n">
+        <v>162.0</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W24" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X24" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA24" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6632,25 +6784,25 @@
         <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="G25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>72</v>
@@ -6682,19 +6834,25 @@
       <c r="T25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U25" s="2" t="b">
+      <c r="U25" s="2" t="n">
+        <v>357.0</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W25" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X25" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA25" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6709,25 +6867,25 @@
         <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="G26" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>72</v>
@@ -6759,52 +6917,58 @@
       <c r="T26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U26" s="2" t="b">
+      <c r="U26" s="2" t="n">
+        <v>133.0</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W26" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X26" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA26" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>72</v>
@@ -6836,43 +7000,49 @@
       <c r="T27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U27" s="2" t="b">
+      <c r="U27" s="2" t="n">
+        <v>915.0</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X27" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA27" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>249</v>
+        <v>114</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
@@ -6881,7 +7051,7 @@
         <v>182</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>72</v>
@@ -6913,52 +7083,58 @@
       <c r="T28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U28" s="2" t="b">
+      <c r="U28" s="2" t="n">
+        <v>371.0</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X28" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA28" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>204</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>72</v>
+        <v>251</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>72</v>
@@ -6990,96 +7166,108 @@
       <c r="T29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U29" s="2" t="b">
+      <c r="U29" s="2" t="n">
+        <v>551.0</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X29" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA29" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>254</v>
+        <v>117</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H30" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>307.0</v>
+      </c>
+      <c r="V30" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U30" s="2" t="b">
+      <c r="W30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA30" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7094,25 +7282,25 @@
         <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>72</v>
@@ -7144,19 +7332,25 @@
       <c r="T31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U31" s="2" t="b">
+      <c r="U31" s="2" t="n">
+        <v>539.0</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W31" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X31" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA31" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7171,25 +7365,25 @@
         <v>74</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>72</v>
@@ -7221,19 +7415,25 @@
       <c r="T32" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U32" s="2" t="b">
+      <c r="U32" s="2" t="n">
+        <v>313.0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W32" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA32" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7248,25 +7448,25 @@
         <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>261</v>
+        <v>120</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>72</v>
@@ -7298,52 +7498,58 @@
       <c r="T33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U33" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>72</v>
+      <c r="U33" s="2" t="n">
+        <v>154.0</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W33" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>72</v>
@@ -7375,52 +7581,58 @@
       <c r="T34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U34" s="2" t="b">
+      <c r="U34" s="2" t="n">
+        <v>799.0</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W34" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X34" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA34" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>268</v>
+        <v>188</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>72</v>
+        <v>251</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>72</v>
@@ -7452,52 +7664,58 @@
       <c r="T35" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U35" s="2" t="b">
+      <c r="U35" s="2" t="n">
+        <v>565.0</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X35" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA35" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>271</v>
+        <v>155</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>72</v>
@@ -7529,52 +7747,58 @@
       <c r="T36" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U36" s="2" t="b">
+      <c r="U36" s="2" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W36" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X36" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA36" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>274</v>
+        <v>125</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>72</v>
@@ -7606,19 +7830,25 @@
       <c r="T37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U37" s="2" t="b">
+      <c r="U37" s="2" t="n">
+        <v>759.0</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W37" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X37" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA37" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7637,7 +7867,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.5859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.27734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.4296875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.25" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="17.625" customWidth="true" bestFit="true"/>
@@ -7645,10 +7875,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2"/>
@@ -7657,16 +7887,16 @@
         <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4">
@@ -7706,7 +7936,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.0</v>
@@ -7806,7 +8036,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -7853,7 +8083,7 @@
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -8140,7 +8370,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -8801,8 +9031,8 @@
       <c r="B18" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>72</v>
+      <c r="C18" s="4" t="s">
+        <v>279</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>72</v>
@@ -9006,8 +9236,8 @@
       <c r="B23" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>284</v>
+      <c r="C23" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>72</v>
@@ -9240,7 +9470,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -9281,13 +9511,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -33,8 +33,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -51,8 +51,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -69,8 +69,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -87,8 +87,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -105,8 +105,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -123,8 +123,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -139,10 +139,10 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C18" authorId="0">
+    <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -159,8 +159,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S31: Understand mobile Angular
-    Flo Poe
+        <t xml:space="preserve">S19: Hack modularized Keycloak
+    Amy Cole
 PINNED BY USER
 </t>
       </text>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="298">
   <si>
     <t>Conference name</t>
   </si>
@@ -424,6 +424,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Capacity</t>
+  </si>
+  <si>
     <t>10:15-12:15</t>
   </si>
   <si>
@@ -454,12 +457,12 @@
     <t>R 3</t>
   </si>
   <si>
+    <t>R 4</t>
+  </si>
+  <si>
     <t>Recorded</t>
   </si>
   <si>
-    <t>R 4</t>
-  </si>
-  <si>
     <t>R 5</t>
   </si>
   <si>
@@ -616,372 +619,396 @@
     <t>Hands on real-time OpenShift</t>
   </si>
   <si>
-    <t>Amy Cole, Beth Fox</t>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Managers</t>
+  </si>
+  <si>
+    <t>OpenShift</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Beth Fox, Chad Green</t>
   </si>
   <si>
     <t>Artificial Intelligence</t>
   </si>
   <si>
-    <t>Managers</t>
-  </si>
-  <si>
-    <t>OpenShift, Kubernetes</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Business analysts</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Middleware, Security</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Mobile, Culture</t>
+  </si>
+  <si>
+    <t>Programmers</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Cloud, Culture</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
   </si>
   <si>
     <t>Cloud</t>
   </si>
   <si>
-    <t>Programmers</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Dan Jones, Elsa King</t>
-  </si>
-  <si>
-    <t>Modern Web, IoT</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Chad Jones, Dan King</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Middleware, Cloud</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
   </si>
   <si>
     <t>Modern Web</t>
   </si>
   <si>
-    <t>Business analysts</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>Modern Web, Cloud</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Security, Middleware</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Chad Green, Dan Jones</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Modern Web, Mobile</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
   </si>
   <si>
     <t>Gus Poe, Hugo Rye</t>
   </si>
   <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
+    <t>Culture, Middleware</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>Ivy Smith, Jay Watt</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>Amy Fox, Beth Green</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
   </si>
   <si>
     <t>Docker, Kubernetes</t>
   </si>
   <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Cloud, Big Data</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Flo Poe, Gus Rye, Hugo Smith</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>Middleware, IoT</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Big Data, Cloud</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Beth Jones, Chad King</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>Modern Web, Big Data</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Beth Fox, Chad Green</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>Telecommunications</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>Dan King, Elsa Li</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Applying modern Weld</t>
+  </si>
+  <si>
+    <t>Ivy Watt, Jay Cole</t>
+  </si>
+  <si>
+    <t>Security, Culture</t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Grok distributed RestEasy</t>
+  </si>
+  <si>
+    <t>Amy Green, Beth Jones</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Android</t>
+  </si>
+  <si>
+    <t>Chad King, Dan Li</t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Using secure Tensorflow</t>
+  </si>
+  <si>
+    <t>Amy Cole, Beth Fox, Chad Green, Dan Jones</t>
   </si>
   <si>
     <t>Healthcare</t>
   </si>
   <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>Amy Fox, Beth Green</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable Hibernate</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise GWT</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Errai</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>Understand mobile Angular</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>Applying modern Weld</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>Grok distributed RestEasy</t>
-  </si>
-  <si>
-    <t>Hugo Smith, Ivy Watt</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable Android</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>Using secure Tensorflow</t>
-  </si>
-  <si>
     <t>Score</t>
   </si>
   <si>
@@ -1003,14 +1030,14 @@
     <t>Total</t>
   </si>
   <si>
-    <t>S31: Understand mobile Angular
-  Flo Poe</t>
+    <t>S19: Hack modularized Keycloak
+  Amy Cole</t>
   </si>
   <si>
     <t>Speaker</t>
   </si>
   <si>
-    <t>S31 @ R 1</t>
+    <t>S19 @ R 1</t>
   </si>
   <si>
     <t>Theme track tag</t>
@@ -1028,7 +1055,7 @@
     <t>Content tag</t>
   </si>
   <si>
-    <t>S31 (level 2)</t>
+    <t>S19 (level 2)</t>
   </si>
   <si>
     <t>Constraint match</t>
@@ -1605,7 +1632,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.6328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
@@ -1663,54 +1690,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>240</v>
+        <v>157</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -1820,43 +1847,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
@@ -1867,7 +1894,7 @@
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -1977,54 +2004,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2134,54 +2161,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2291,43 +2318,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
@@ -2338,43 +2365,43 @@
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="O3" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -2404,13 +2431,13 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2664,9 +2691,9 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.87890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.140625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="10.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.87890625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="16.140625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
@@ -2678,6 +2705,7 @@
     <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="15" max="15" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2732,13 +2760,13 @@
         <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>85</v>
@@ -2756,7 +2784,7 @@
         <v>89</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>85</v>
@@ -2773,19 +2801,22 @@
       <c r="O2" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>72</v>
@@ -2818,19 +2849,22 @@
         <v>72</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D4" s="2" t="s">
         <v>72</v>
       </c>
@@ -2865,21 +2899,24 @@
         <v>72</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>630.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>72</v>
@@ -2912,6 +2949,9 @@
         <v>72</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2919,14 +2959,14 @@
       <c r="A6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="2" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>72</v>
@@ -2959,21 +2999,24 @@
         <v>72</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>490.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>72</v>
@@ -3006,6 +3049,9 @@
         <v>72</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3117,69 +3163,69 @@
         <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="U2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>72</v>
@@ -3244,7 +3290,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>72</v>
@@ -3309,7 +3355,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>72</v>
@@ -3327,7 +3373,7 @@
         <v>72</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>72</v>
@@ -3374,7 +3420,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>72</v>
@@ -3439,7 +3485,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>72</v>
@@ -3504,7 +3550,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>72</v>
@@ -3530,13 +3576,13 @@
       <c r="I8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="J8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="M8" s="2" t="s">
@@ -3548,13 +3594,13 @@
       <c r="O8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R8" s="2" t="s">
+      <c r="P8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="S8" s="2" t="s">
@@ -3569,7 +3615,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>72</v>
@@ -3587,7 +3633,7 @@
         <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>72</v>
@@ -3634,7 +3680,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>72</v>
@@ -3699,7 +3745,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>72</v>
@@ -3725,13 +3771,13 @@
       <c r="I11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="3" t="s">
+      <c r="J11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="M11" s="2" t="s">
@@ -3743,13 +3789,13 @@
       <c r="O11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="P11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="S11" s="2" t="s">
@@ -3764,7 +3810,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>72</v>
@@ -3782,7 +3828,7 @@
         <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>72</v>
@@ -3829,7 +3875,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>72</v>
@@ -3894,7 +3940,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>72</v>
@@ -3959,7 +4005,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>72</v>
@@ -3974,7 +4020,7 @@
         <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>72</v>
@@ -4024,7 +4070,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>72</v>
@@ -4089,7 +4135,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>72</v>
@@ -4154,7 +4200,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>72</v>
@@ -4219,7 +4265,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>72</v>
@@ -4284,7 +4330,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>72</v>
@@ -4349,7 +4395,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>72</v>
@@ -4414,7 +4460,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>72</v>
@@ -4446,16 +4492,16 @@
       <c r="K22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" s="2" t="s">
         <v>72</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O22" s="3" t="s">
+      <c r="N22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>72</v>
       </c>
       <c r="P22" s="2" t="s">
@@ -4479,7 +4525,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>72</v>
@@ -4508,7 +4554,7 @@
       <c r="J23" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L23" s="2" t="s">
@@ -4544,7 +4590,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>72</v>
@@ -4609,7 +4655,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>72</v>
@@ -4674,7 +4720,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>72</v>
@@ -4755,12 +4801,12 @@
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.3125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="28.3515625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="21.6953125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="20.05859375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="41.48828125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="20.296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="17.30859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.34375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.3046875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="21.8046875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="19.1953125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="11.3046875" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="24.85546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="25.390625" customWidth="true" bestFit="true"/>
@@ -4783,76 +4829,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>64</v>
@@ -4861,21 +4907,21 @@
         <v>65</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>149</v>
@@ -4926,10 +4972,10 @@
         <v>72</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>639.0</v>
+        <v>546.0</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W2" s="2" t="b">
         <v>0</v>
@@ -4958,22 +5004,22 @@
         <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>152</v>
@@ -5009,10 +5055,10 @@
         <v>72</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>357.0</v>
+        <v>785.0</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W3" s="2" t="b">
         <v>0</v>
@@ -5032,19 +5078,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>72</v>
@@ -5053,7 +5099,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>162</v>
@@ -5092,10 +5138,10 @@
         <v>72</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>945.0</v>
+        <v>245.0</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W4" s="2" t="b">
         <v>0</v>
@@ -5130,13 +5176,13 @@
         <v>165</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>167</v>
@@ -5175,7 +5221,7 @@
         <v>72</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>325.0</v>
+        <v>156.0</v>
       </c>
       <c r="V5" s="2" t="n">
         <v>1.0</v>
@@ -5207,19 +5253,19 @@
         <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="H6" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>172</v>
@@ -5258,10 +5304,10 @@
         <v>72</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>724.0</v>
+        <v>318.0</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W6" s="2" t="b">
         <v>0</v>
@@ -5290,7 +5336,7 @@
         <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>175</v>
@@ -5299,10 +5345,10 @@
         <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>176</v>
@@ -5341,10 +5387,10 @@
         <v>72</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>259.0</v>
+        <v>56.0</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W7" s="2" t="b">
         <v>0</v>
@@ -5373,22 +5419,22 @@
         <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>152</v>
@@ -5424,10 +5470,10 @@
         <v>72</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>500.0</v>
+        <v>596.0</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="W8" s="2" t="b">
         <v>0</v>
@@ -5447,31 +5493,31 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>152</v>
@@ -5507,10 +5553,10 @@
         <v>72</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>558.0</v>
+        <v>701.0</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W9" s="2" t="b">
         <v>0</v>
@@ -5530,31 +5576,31 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>152</v>
@@ -5590,10 +5636,10 @@
         <v>72</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>264.0</v>
+        <v>77.0</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W10" s="2" t="b">
         <v>0</v>
@@ -5613,31 +5659,31 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>152</v>
@@ -5673,10 +5719,10 @@
         <v>72</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>144.0</v>
+        <v>492.0</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="W11" s="2" t="b">
         <v>0</v>
@@ -5696,31 +5742,31 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>152</v>
@@ -5756,7 +5802,7 @@
         <v>72</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>840.0</v>
+        <v>623.0</v>
       </c>
       <c r="V12" s="2" t="n">
         <v>2.0</v>
@@ -5779,31 +5825,31 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>152</v>
@@ -5839,10 +5885,10 @@
         <v>72</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>201.0</v>
+        <v>789.0</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W13" s="2" t="b">
         <v>0</v>
@@ -5862,31 +5908,31 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>152</v>
@@ -5922,10 +5968,10 @@
         <v>72</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>543.0</v>
+        <v>206.0</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W14" s="2" t="b">
         <v>0</v>
@@ -5945,31 +5991,31 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>152</v>
@@ -6005,10 +6051,10 @@
         <v>72</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>973.0</v>
+        <v>950.0</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W15" s="2" t="b">
         <v>0</v>
@@ -6028,31 +6074,31 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>152</v>
@@ -6088,10 +6134,10 @@
         <v>72</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>74.0</v>
+        <v>995.0</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="W16" s="2" t="b">
         <v>0</v>
@@ -6111,10 +6157,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>74</v>
@@ -6123,19 +6169,19 @@
         <v>125</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>152</v>
@@ -6171,10 +6217,10 @@
         <v>72</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>871.0</v>
+        <v>530.0</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="W17" s="2" t="b">
         <v>0</v>
@@ -6194,31 +6240,31 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>152</v>
@@ -6254,7 +6300,7 @@
         <v>72</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>411.0</v>
+        <v>529.0</v>
       </c>
       <c r="V18" s="2" t="n">
         <v>3.0</v>
@@ -6277,31 +6323,31 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>152</v>
@@ -6337,10 +6383,10 @@
         <v>72</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>118.0</v>
+        <v>715.0</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="W19" s="2" t="b">
         <v>0</v>
@@ -6360,31 +6406,31 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>152</v>
@@ -6420,10 +6466,10 @@
         <v>72</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>320.0</v>
+        <v>516.0</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W20" s="2" t="b">
         <v>0</v>
@@ -6443,22 +6489,22 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>229</v>
+        <v>157</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>150</v>
@@ -6467,7 +6513,7 @@
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>152</v>
@@ -6503,42 +6549,42 @@
         <v>72</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>142.0</v>
+        <v>43.0</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="W21" s="2" t="b">
-        <v>0</v>
+        <v>2.0</v>
+      </c>
+      <c r="W21" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>72</v>
@@ -6547,10 +6593,10 @@
         <v>150</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>152</v>
@@ -6586,7 +6632,7 @@
         <v>72</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>287.0</v>
+        <v>445.0</v>
       </c>
       <c r="V22" s="2" t="n">
         <v>0.0</v>
@@ -6609,25 +6655,25 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>109</v>
+        <v>236</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>235</v>
+        <v>72</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1.0</v>
@@ -6669,10 +6715,10 @@
         <v>72</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>435.0</v>
+        <v>289.0</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W23" s="2" t="b">
         <v>0</v>
@@ -6692,10 +6738,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>74</v>
@@ -6704,16 +6750,16 @@
         <v>110</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>167</v>
@@ -6752,10 +6798,10 @@
         <v>72</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>162.0</v>
+        <v>229.0</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="W24" s="2" t="b">
         <v>0</v>
@@ -6775,10 +6821,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>74</v>
@@ -6787,16 +6833,16 @@
         <v>111</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>172</v>
@@ -6835,10 +6881,10 @@
         <v>72</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>357.0</v>
+        <v>915.0</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="W25" s="2" t="b">
         <v>0</v>
@@ -6858,28 +6904,28 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>112</v>
+        <v>244</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>243</v>
+        <v>72</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>176</v>
@@ -6918,10 +6964,10 @@
         <v>72</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>133.0</v>
+        <v>466.0</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W26" s="2" t="b">
         <v>0</v>
@@ -6941,31 +6987,31 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>113</v>
+        <v>248</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>152</v>
@@ -7001,10 +7047,10 @@
         <v>72</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>915.0</v>
+        <v>388.0</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="W27" s="2" t="b">
         <v>0</v>
@@ -7024,31 +7070,31 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>114</v>
+        <v>251</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>152</v>
@@ -7084,10 +7130,10 @@
         <v>72</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>371.0</v>
+        <v>32.0</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W28" s="2" t="b">
         <v>0</v>
@@ -7107,31 +7153,31 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>251</v>
+        <v>72</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>150</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>152</v>
@@ -7167,7 +7213,7 @@
         <v>72</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>551.0</v>
+        <v>558.0</v>
       </c>
       <c r="V29" s="2" t="n">
         <v>0.0</v>
@@ -7190,31 +7236,31 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>117</v>
+        <v>257</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>152</v>
@@ -7250,10 +7296,10 @@
         <v>72</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>307.0</v>
+        <v>119.0</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W30" s="2" t="b">
         <v>0</v>
@@ -7273,31 +7319,31 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>229</v>
+        <v>72</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>152</v>
@@ -7333,10 +7379,10 @@
         <v>72</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>539.0</v>
+        <v>838.0</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W31" s="2" t="b">
         <v>0</v>
@@ -7356,31 +7402,31 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>152</v>
@@ -7416,7 +7462,7 @@
         <v>72</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>313.0</v>
+        <v>734.0</v>
       </c>
       <c r="V32" s="2" t="n">
         <v>0.0</v>
@@ -7439,22 +7485,22 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>150</v>
@@ -7463,7 +7509,7 @@
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>152</v>
@@ -7499,54 +7545,54 @@
         <v>72</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>154.0</v>
+        <v>888.0</v>
       </c>
       <c r="V33" s="2" t="n">
         <v>0.0</v>
       </c>
-      <c r="W33" s="4" t="b">
-        <v>1</v>
+      <c r="W33" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>121</v>
+        <v>266</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>152</v>
@@ -7582,10 +7628,10 @@
         <v>72</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>799.0</v>
+        <v>421.0</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="W34" s="2" t="b">
         <v>0</v>
@@ -7605,31 +7651,31 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>251</v>
+        <v>72</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>152</v>
@@ -7665,10 +7711,10 @@
         <v>72</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>565.0</v>
+        <v>109.0</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W35" s="2" t="b">
         <v>0</v>
@@ -7688,31 +7734,31 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>124</v>
+        <v>274</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>152</v>
@@ -7748,10 +7794,10 @@
         <v>72</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>128.0</v>
+        <v>464.0</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W36" s="2" t="b">
         <v>0</v>
@@ -7771,31 +7817,31 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>125</v>
+        <v>277</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>72</v>
+        <v>278</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>152</v>
@@ -7831,10 +7877,10 @@
         <v>72</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>759.0</v>
+        <v>751.0</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W37" s="2" t="b">
         <v>0</v>
@@ -7875,28 +7921,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4">
@@ -7936,7 +7982,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.0</v>
@@ -8036,54 +8082,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -8118,7 +8164,7 @@
     </row>
     <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>72</v>
@@ -8159,7 +8205,7 @@
     </row>
     <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>72</v>
@@ -8241,7 +8287,7 @@
     </row>
     <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>72</v>
@@ -8370,54 +8416,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>72</v>
+      <c r="C3" s="4" t="s">
+        <v>288</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -8452,7 +8498,7 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>72</v>
@@ -8493,7 +8539,7 @@
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>72</v>
@@ -8534,7 +8580,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>72</v>
@@ -8575,7 +8621,7 @@
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>72</v>
@@ -8616,15 +8662,15 @@
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -8636,13 +8682,13 @@
       <c r="G8" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="H8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="K8" s="8" t="s">
@@ -8657,7 +8703,7 @@
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>72</v>
@@ -8698,7 +8744,7 @@
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>72</v>
@@ -8739,15 +8785,15 @@
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -8759,13 +8805,13 @@
       <c r="G11" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="H11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>72</v>
       </c>
       <c r="K11" s="8" t="s">
@@ -8780,7 +8826,7 @@
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>72</v>
@@ -8821,7 +8867,7 @@
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>72</v>
@@ -8862,7 +8908,7 @@
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>72</v>
@@ -8903,7 +8949,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>72</v>
@@ -8944,7 +8990,7 @@
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>72</v>
@@ -8985,7 +9031,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>72</v>
@@ -9026,13 +9072,13 @@
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>279</v>
+      <c r="C18" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>72</v>
@@ -9067,7 +9113,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>72</v>
@@ -9108,7 +9154,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>72</v>
@@ -9149,7 +9195,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>72</v>
@@ -9190,7 +9236,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>72</v>
@@ -9198,16 +9244,16 @@
       <c r="C22" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="F22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>72</v>
       </c>
       <c r="H22" s="8" t="s">
@@ -9231,12 +9277,12 @@
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="8" t="s">
         <v>72</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -9272,7 +9318,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>72</v>
@@ -9313,7 +9359,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>72</v>
@@ -9354,7 +9400,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>72</v>
@@ -9470,54 +9516,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>230</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="300">
   <si>
     <t>Conference name</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>Soft penalty per common content/theme of 2 talks that are scheduled on different days</t>
+  </si>
+  <si>
+    <t>Popular talks</t>
+  </si>
+  <si>
+    <t>Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
   </si>
   <si>
     <t>Talk type of timeslot</t>
@@ -1441,18 +1447,18 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="1" t="s">
+    <row r="21">
+      <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="B21" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>36</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="1" t="s">
         <v>37</v>
@@ -1480,7 +1486,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>10.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>42</v>
@@ -1491,7 +1497,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>44</v>
@@ -1538,12 +1544,12 @@
         <v>1.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1.0</v>
@@ -1554,13 +1560,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33">
@@ -1582,12 +1588,12 @@
         <v>1.0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1.0</v>
@@ -1598,13 +1604,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37">
@@ -1616,6 +1622,17 @@
       </c>
       <c r="C37" s="1" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1649,125 +1666,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1806,125 +1823,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1963,125 +1980,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2120,125 +2137,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2277,131 +2294,131 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -2431,13 +2448,13 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -2460,223 +2477,223 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2710,355 +2727,358 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>60.0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>240.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>630.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>70.0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>490.0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="K1:P1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
@@ -3095,1692 +3115,1692 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -4829,147 +4849,147 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>546.0</v>
@@ -4981,78 +5001,78 @@
         <v>0</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>785.0</v>
@@ -5064,78 +5084,78 @@
         <v>0</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>245.0</v>
@@ -5147,78 +5167,78 @@
         <v>0</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>156.0</v>
@@ -5230,78 +5250,78 @@
         <v>0</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>318.0</v>
@@ -5313,78 +5333,78 @@
         <v>0</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>56.0</v>
@@ -5396,78 +5416,78 @@
         <v>0</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>596.0</v>
@@ -5479,78 +5499,78 @@
         <v>0</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>701.0</v>
@@ -5562,78 +5582,78 @@
         <v>0</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>77.0</v>
@@ -5645,78 +5665,78 @@
         <v>0</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>492.0</v>
@@ -5728,78 +5748,78 @@
         <v>0</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>623.0</v>
@@ -5811,78 +5831,78 @@
         <v>0</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>789.0</v>
@@ -5894,78 +5914,78 @@
         <v>0</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>206.0</v>
@@ -5977,78 +5997,78 @@
         <v>0</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>950.0</v>
@@ -6060,78 +6080,78 @@
         <v>0</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>995.0</v>
@@ -6143,78 +6163,78 @@
         <v>0</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U17" s="2" t="n">
         <v>530.0</v>
@@ -6226,78 +6246,78 @@
         <v>0</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>529.0</v>
@@ -6309,78 +6329,78 @@
         <v>0</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>715.0</v>
@@ -6392,78 +6412,78 @@
         <v>0</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>516.0</v>
@@ -6475,78 +6495,78 @@
         <v>0</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U21" s="2" t="n">
         <v>43.0</v>
@@ -6558,78 +6578,78 @@
         <v>1</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>445.0</v>
@@ -6641,78 +6661,78 @@
         <v>0</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>289.0</v>
@@ -6724,78 +6744,78 @@
         <v>0</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>229.0</v>
@@ -6807,78 +6827,78 @@
         <v>0</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>915.0</v>
@@ -6890,78 +6910,78 @@
         <v>0</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>466.0</v>
@@ -6973,78 +6993,78 @@
         <v>0</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>388.0</v>
@@ -7056,78 +7076,78 @@
         <v>0</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U28" s="2" t="n">
         <v>32.0</v>
@@ -7139,78 +7159,78 @@
         <v>0</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U29" s="2" t="n">
         <v>558.0</v>
@@ -7222,78 +7242,78 @@
         <v>0</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U30" s="2" t="n">
         <v>119.0</v>
@@ -7305,78 +7325,78 @@
         <v>0</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U31" s="2" t="n">
         <v>838.0</v>
@@ -7388,78 +7408,78 @@
         <v>0</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U32" s="2" t="n">
         <v>734.0</v>
@@ -7471,78 +7491,78 @@
         <v>0</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U33" s="2" t="n">
         <v>888.0</v>
@@ -7554,78 +7574,78 @@
         <v>0</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U34" s="2" t="n">
         <v>421.0</v>
@@ -7637,78 +7657,78 @@
         <v>0</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U35" s="2" t="n">
         <v>109.0</v>
@@ -7720,78 +7740,78 @@
         <v>0</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U36" s="2" t="n">
         <v>464.0</v>
@@ -7803,78 +7823,78 @@
         <v>0</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U37" s="2" t="n">
         <v>751.0</v>
@@ -7886,16 +7906,16 @@
         <v>0</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -7921,33 +7941,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>4.0</v>
@@ -7964,7 +7984,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>32.0</v>
@@ -7982,7 +8002,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.0</v>
@@ -8041,289 +8061,289 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -8375,1068 +8395,1068 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -9475,125 +9495,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -235,40 +235,40 @@
     <t>Soft reward per 2 talks that have the same timeslot and a different language</t>
   </si>
   <si>
-    <t>Speaker preferred timeslot tag</t>
+    <t>Speaker preferred timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker undesired timeslot tag</t>
+    <t>Speaker undesired timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk preferred timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk undesired timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker preferred room tag</t>
+    <t>Talk preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker preferred room tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker undesired room tag</t>
+    <t>Speaker undesired room tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk preferred room tag</t>
-  </si>
-  <si>
-    <t>Talk undesired room tag</t>
+    <t>Talk preferred room tags</t>
+  </si>
+  <si>
+    <t>Talk undesired room tags</t>
   </si>
   <si>
     <t>Same day talks</t>
@@ -319,43 +319,43 @@
     <t>Hard penalty per pair of talks with the same speaker in overlapping timeslots</t>
   </si>
   <si>
-    <t>Speaker required timeslot tag</t>
+    <t>Speaker required timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker prohibited timeslot tag</t>
+    <t>Speaker prohibited timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk required timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker required room tag</t>
+    <t>Talk required timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker required room tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker prohibited room tag</t>
+    <t>Speaker prohibited room tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk required room tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited room tag</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tag</t>
+    <t>Talk required room tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited room tags</t>
+  </si>
+  <si>
+    <t>Talk mutually-exclusive-talks tags</t>
   </si>
   <si>
     <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -36,6 +36,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -54,6 +56,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -72,6 +76,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -90,6 +96,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -108,6 +116,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -126,6 +136,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -144,6 +156,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -162,6 +176,8 @@
         <t xml:space="preserve">S19: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
+-10soft total
+    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -170,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="304">
   <si>
     <t>Conference name</t>
   </si>
@@ -283,6 +299,12 @@
     <t>Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
   </si>
   <si>
+    <t>Crowd control</t>
+  </si>
+  <si>
+    <t>Soft penalty per talks with crowd control risk greater than zero that are not in pairs</t>
+  </si>
+  <si>
     <t>Talk type of timeslot</t>
   </si>
   <si>
@@ -1018,7 +1040,7 @@
     <t>Score</t>
   </si>
   <si>
-    <t>-70init</t>
+    <t>-70init/-10soft</t>
   </si>
   <si>
     <t>Count</t>
@@ -1071,6 +1093,12 @@
   </si>
   <si>
     <t>Total score</t>
+  </si>
+  <si>
+    <t>-10soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    S19</t>
   </si>
 </sst>
 </file>
@@ -1458,18 +1486,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="1" t="s">
+    <row r="22">
+      <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="B22" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="s">
         <v>39</v>
@@ -1497,7 +1525,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>10.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>44</v>
@@ -1508,7 +1536,7 @@
         <v>45</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>46</v>
@@ -1555,12 +1583,12 @@
         <v>1.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1.0</v>
@@ -1571,13 +1599,13 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34">
@@ -1599,12 +1627,12 @@
         <v>1.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1.0</v>
@@ -1615,13 +1643,13 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
@@ -1633,6 +1661,17 @@
       </c>
       <c r="C38" s="1" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1666,125 +1705,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1823,125 +1862,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1980,125 +2019,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2137,125 +2176,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2294,131 +2333,131 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -2448,14 +2487,33 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
-      </c>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2477,223 +2535,223 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2727,352 +2785,352 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>60.0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>240.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>630.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>70.0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>490.0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3115,1692 +3173,1692 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -4849,147 +4907,147 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>546.0</v>
@@ -5001,78 +5059,78 @@
         <v>0</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>785.0</v>
@@ -5084,78 +5142,78 @@
         <v>0</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>245.0</v>
@@ -5167,78 +5225,78 @@
         <v>0</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>156.0</v>
@@ -5250,78 +5308,78 @@
         <v>0</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>318.0</v>
@@ -5333,78 +5391,78 @@
         <v>0</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>56.0</v>
@@ -5416,78 +5474,78 @@
         <v>0</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>596.0</v>
@@ -5499,78 +5557,78 @@
         <v>0</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>701.0</v>
@@ -5582,78 +5640,78 @@
         <v>0</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>77.0</v>
@@ -5665,78 +5723,78 @@
         <v>0</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>492.0</v>
@@ -5748,78 +5806,78 @@
         <v>0</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>623.0</v>
@@ -5831,78 +5889,78 @@
         <v>0</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>789.0</v>
@@ -5914,78 +5972,78 @@
         <v>0</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>206.0</v>
@@ -5997,78 +6055,78 @@
         <v>0</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>950.0</v>
@@ -6080,78 +6138,78 @@
         <v>0</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>995.0</v>
@@ -6163,78 +6221,78 @@
         <v>0</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U17" s="2" t="n">
         <v>530.0</v>
@@ -6246,78 +6304,78 @@
         <v>0</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>529.0</v>
@@ -6329,78 +6387,78 @@
         <v>0</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>715.0</v>
@@ -6412,78 +6470,78 @@
         <v>0</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>516.0</v>
@@ -6495,78 +6553,78 @@
         <v>0</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U21" s="2" t="n">
         <v>43.0</v>
@@ -6578,78 +6636,78 @@
         <v>1</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>445.0</v>
@@ -6661,78 +6719,78 @@
         <v>0</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>289.0</v>
@@ -6744,78 +6802,78 @@
         <v>0</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>229.0</v>
@@ -6827,78 +6885,78 @@
         <v>0</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>915.0</v>
@@ -6910,78 +6968,78 @@
         <v>0</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>466.0</v>
@@ -6993,78 +7051,78 @@
         <v>0</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>388.0</v>
@@ -7076,78 +7134,78 @@
         <v>0</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U28" s="2" t="n">
         <v>32.0</v>
@@ -7159,78 +7217,78 @@
         <v>0</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U29" s="2" t="n">
         <v>558.0</v>
@@ -7242,78 +7300,78 @@
         <v>0</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U30" s="2" t="n">
         <v>119.0</v>
@@ -7325,78 +7383,78 @@
         <v>0</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U31" s="2" t="n">
         <v>838.0</v>
@@ -7408,78 +7466,78 @@
         <v>0</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U32" s="2" t="n">
         <v>734.0</v>
@@ -7491,78 +7549,78 @@
         <v>0</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U33" s="2" t="n">
         <v>888.0</v>
@@ -7574,78 +7632,78 @@
         <v>0</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U34" s="2" t="n">
         <v>421.0</v>
@@ -7657,78 +7715,78 @@
         <v>0</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U35" s="2" t="n">
         <v>109.0</v>
@@ -7740,78 +7798,78 @@
         <v>0</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U36" s="2" t="n">
         <v>464.0</v>
@@ -7823,78 +7881,78 @@
         <v>0</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U37" s="2" t="n">
         <v>751.0</v>
@@ -7906,16 +7964,16 @@
         <v>0</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -7933,7 +7991,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.27734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.98828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.4296875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.25" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="17.625" customWidth="true" bestFit="true"/>
@@ -7941,33 +7999,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>4.0</v>
@@ -7984,7 +8042,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>32.0</v>
@@ -8002,7 +8060,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.0</v>
@@ -8061,289 +8119,289 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -8395,1068 +8453,1068 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -9495,125 +9553,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -296,7 +296,7 @@
     <t>Popular talks</t>
   </si>
   <si>
-    <t>Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
+    <t>Soft penalty per 2 talks where the less popular one (has lower favorite count) is assigned a larger room than the more popular talk</t>
   </si>
   <si>
     <t>Crowd control</t>
@@ -626,7 +626,7 @@
     <t>Prerequisite talks codes</t>
   </si>
   <si>
-    <t>Number of likes</t>
+    <t>Favorite count</t>
   </si>
   <si>
     <t>Crowd control risk</t>
@@ -4896,7 +4896,7 @@
     <col min="18" max="18" width="22.84375" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="31.2734375" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="26.23046875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.5390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="16.25390625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="20.140625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.65234375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.14453125" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -21,6 +21,8 @@
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
     <sheet name="Languages view" r:id="rId16" sheetId="14"/>
     <sheet name="Score view" r:id="rId17" sheetId="15"/>
+    <sheet name="Mon 2018-10-01" r:id="rId18" sheetId="16"/>
+    <sheet name="Tue 2018-10-02" r:id="rId19" sheetId="17"/>
   </sheets>
 </workbook>
 </file>
@@ -33,11 +35,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -53,11 +54,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -73,11 +73,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -93,11 +92,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -113,7 +111,26 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
+    Amy Cole
+PINNED BY USER
+-10soft total
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
@@ -133,7 +150,7 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
@@ -153,11 +170,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -173,11 +189,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19: Hack modularized Keycloak
+        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
     Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -186,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2351" uniqueCount="305">
   <si>
     <t>Conference name</t>
   </si>
@@ -305,6 +320,12 @@
     <t>Soft penalty per talks with crowd control risk greater than zero that are not in pairs</t>
   </si>
   <si>
+    <t>Talk mutually-exclusive-talks tags</t>
+  </si>
+  <si>
+    <t>Medium penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
+  </si>
+  <si>
     <t>Talk type of timeslot</t>
   </si>
   <si>
@@ -375,12 +396,6 @@
   </si>
   <si>
     <t>Talk prohibited room tags</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tags</t>
-  </si>
-  <si>
-    <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
   </si>
   <si>
     <t>Talk prerequisite talks</t>
@@ -1099,6 +1114,10 @@
   </si>
   <si>
     <t xml:space="preserve">    S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak
+Amy Cole</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1139,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1155,6 +1174,46 @@
         <fgColor rgb="FCAF3E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="8AE234"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCE94F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="729FCF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="E9B96E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="73D216"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="EDD400"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="3465A4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="C17D11"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1168,7 +1227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment wrapText="true" vertical="center"/>
@@ -1192,6 +1251,33 @@
       <alignment wrapText="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1223,6 +1309,14 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
@@ -1260,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.66796875" customWidth="true" bestFit="true"/>
@@ -1503,109 +1597,99 @@
         <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10000.0</v>
+        <v>1.0</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>10000.0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>10.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -1616,40 +1700,40 @@
         <v>1.0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -1660,17 +1744,28 @@
         <v>1.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1685,7 +1780,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="true" bestFit="true"/>
@@ -1842,7 +1937,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
@@ -1999,7 +2094,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.3046875" customWidth="true" bestFit="true"/>
@@ -2156,7 +2251,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="13.4609375" customWidth="true" bestFit="true"/>
@@ -2313,7 +2408,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.3046875" customWidth="true" bestFit="true"/>
@@ -2453,12 +2548,6 @@
       <c r="M3" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>284</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -2476,44 +2565,179 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.0703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.98828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="4">
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.3515625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2523,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.14453125" customWidth="true" bestFit="true"/>
@@ -2762,7 +2986,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
@@ -3145,7 +3369,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
@@ -4873,7 +5097,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
@@ -7987,7 +8211,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.78515625" customWidth="true" bestFit="true"/>
@@ -8086,7 +8310,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.02734375" customWidth="true" bestFit="true"/>
@@ -8420,7 +8644,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
@@ -9533,7 +9757,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -27,25 +27,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0">
-      <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
-PINNED BY USER
--45hard total
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -54,10 +35,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -73,10 +53,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -92,10 +71,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -111,10 +89,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -130,11 +107,9 @@
   <commentList>
     <comment ref="B3" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
-    -45hard for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -150,11 +125,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
-    -45hard for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -168,12 +141,11 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0">
+    <comment ref="C15" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -189,10 +161,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S19-Culture: Hack modularized Keycloak
-    Amy Cole
+        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
+    Chad Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -201,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2767" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2752" uniqueCount="334">
   <si>
     <t>Conference name</t>
   </si>
@@ -743,343 +714,343 @@
     <t>Advanced containerized WildFly</t>
   </si>
   <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Business analysts</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Chad Green, Dan Jones</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Programmers</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Elsa King, Flo Li</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Gus Poe, Hugo Rye</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Dan King, Elsa Li</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Gus Rye, Hugo Smith</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>Jay Cole, Amy Green, Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Ivy Smith, Jay Watt</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>Beth Green, Chad Jones</t>
+  </si>
+  <si>
+    <t>Modern Web, IoT</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
+  </si>
+  <si>
+    <t>Big Data, Culture</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
+    <t>Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>Culture, Middleware</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>Jay Cole, Amy Green</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>Dan Li, Amy Cole</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
     <t>Beth Fox, Chad Green</t>
   </si>
   <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Business analysts</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Middleware, Security</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Mobile, Culture</t>
-  </si>
-  <si>
-    <t>Programmers</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Cloud, Culture</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Chad Jones, Dan King</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Middleware, Cloud</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Flo Poe, Gus Rye</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>Hugo Smith, Ivy Watt</t>
-  </si>
-  <si>
-    <t>Modern Web, Cloud</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>Beth Jones, Chad King</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>Security, Middleware</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Chad Green, Dan Jones</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Modern Web, Mobile</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>Gus Poe, Hugo Rye</t>
-  </si>
-  <si>
-    <t>Culture, Middleware</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>Ivy Smith, Jay Watt</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Amy Fox, Beth Green</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>Docker, Kubernetes</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable Hibernate</t>
-  </si>
-  <si>
-    <t>Dan King, Elsa Li</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise GWT</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Errai</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>Understand mobile Angular</t>
-  </si>
-  <si>
     <t>S32</t>
   </si>
   <si>
     <t>Applying modern Weld</t>
   </si>
   <si>
-    <t>Ivy Watt, Jay Cole</t>
-  </si>
-  <si>
-    <t>Security, Culture</t>
+    <t>Dan Jones, Elsa King</t>
   </si>
   <si>
     <t>S33</t>
@@ -1088,37 +1059,25 @@
     <t>Grok distributed RestEasy</t>
   </si>
   <si>
-    <t>Amy Green, Beth Jones</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
     <t>S34</t>
   </si>
   <si>
     <t>Troubleshooting reliable Android</t>
   </si>
   <si>
-    <t>Chad King, Dan Li</t>
-  </si>
-  <si>
     <t>S35</t>
   </si>
   <si>
     <t>Using secure Tensorflow</t>
   </si>
   <si>
-    <t>Amy Cole, Beth Fox, Chad Green, Dan Jones</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
+    <t>Modern Web, Middleware</t>
   </si>
   <si>
     <t>Score</t>
   </si>
   <si>
-    <t>-70init/-45hard</t>
+    <t>-70init</t>
   </si>
   <si>
     <t>Count</t>
@@ -1136,14 +1095,14 @@
     <t>Total</t>
   </si>
   <si>
-    <t>S19: Hack modularized Keycloak
-  Amy Cole</t>
+    <t>S09: Debug enterprise Hibernate
+  Chad Jones</t>
   </si>
   <si>
     <t>Speaker</t>
   </si>
   <si>
-    <t>S19 @ R 1</t>
+    <t>S09 @ R 1</t>
   </si>
   <si>
     <t>Theme track tag</t>
@@ -1155,13 +1114,13 @@
     <t>Audience type</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Content tag</t>
   </si>
   <si>
-    <t>S19 (level 2)</t>
+    <t>S09 (level 3)</t>
   </si>
   <si>
     <t>Constraint name</t>
@@ -1200,9 +1159,6 @@
     <t>1hard</t>
   </si>
   <si>
-    <t>-45hard</t>
-  </si>
-  <si>
     <t>1medium</t>
   </si>
   <si>
@@ -1218,8 +1174,8 @@
     <t>1soft</t>
   </si>
   <si>
-    <t>Hack modularized Keycloak
-Amy Cole</t>
+    <t>Debug enterprise Hibernate
+Chad Jones</t>
   </si>
 </sst>
 </file>
@@ -1934,10 +1890,10 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -1995,7 +1951,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2032,47 +1988,6 @@
       </c>
       <c r="M2" s="1" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="3" ht="15.0" customHeight="true">
-      <c r="A3" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2082,7 +1997,6 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2152,7 +2066,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2199,7 +2113,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2350,13 +2264,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2466,7 +2380,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2507,13 +2421,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2670,7 +2584,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2719,13 +2633,13 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="17.34375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.65234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="8.0703125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="6.0859375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="1.0546875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.296875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="12.9296875" customWidth="true" bestFit="true"/>
@@ -2733,39 +2647,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2778,13 +2692,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6">
@@ -2792,13 +2706,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7">
@@ -2806,13 +2720,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8">
@@ -2820,13 +2734,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2834,13 +2748,13 @@
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -2848,13 +2762,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -2862,13 +2776,13 @@
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12">
@@ -2876,13 +2790,13 @@
         <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13">
@@ -2890,13 +2804,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14">
@@ -2904,13 +2818,13 @@
         <v>34</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15">
@@ -2918,13 +2832,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16">
@@ -2932,13 +2846,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17">
@@ -2946,13 +2860,13 @@
         <v>39</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18">
@@ -2960,13 +2874,13 @@
         <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19">
@@ -2974,13 +2888,13 @@
         <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20">
@@ -2988,13 +2902,13 @@
         <v>32</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21">
@@ -3002,13 +2916,13 @@
         <v>40</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22">
@@ -3016,13 +2930,13 @@
         <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23">
@@ -3030,13 +2944,13 @@
         <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24">
@@ -3044,13 +2958,13 @@
         <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25">
@@ -3058,13 +2972,13 @@
         <v>80</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26">
@@ -3072,13 +2986,13 @@
         <v>74</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27">
@@ -3086,13 +3000,13 @@
         <v>82</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28">
@@ -3100,13 +3014,13 @@
         <v>76</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29">
@@ -3114,13 +3028,13 @@
         <v>83</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30">
@@ -3128,13 +3042,13 @@
         <v>77</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31">
@@ -3142,13 +3056,13 @@
         <v>60</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32">
@@ -3156,13 +3070,13 @@
         <v>65</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33">
@@ -3170,13 +3084,13 @@
         <v>69</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34">
@@ -3184,13 +3098,13 @@
         <v>43</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35">
@@ -3198,13 +3112,13 @@
         <v>67</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36">
@@ -3212,13 +3126,13 @@
         <v>50</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37">
@@ -3226,13 +3140,13 @@
         <v>46</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38">
@@ -3240,13 +3154,13 @@
         <v>48</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39">
@@ -3254,13 +3168,13 @@
         <v>58</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40">
@@ -3268,13 +3182,13 @@
         <v>52</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41">
@@ -3282,243 +3196,244 @@
         <v>55</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42"/>
     <row r="43"/>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>253</v>
+      <c r="C45" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>330</v>
@@ -3527,301 +3442,287 @@
         <v>0.0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3862,8 +3763,8 @@
       <c r="A3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>338</v>
+      <c r="B3" s="18" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="4" ht="45.0" customHeight="true">
@@ -6315,8 +6216,8 @@
     <col min="1" max="1" width="5.69140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.7734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.41796875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="40.00390625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.3046875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="39.91015625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="24.78515625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="16.515625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="16.4453125" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.4375" customWidth="true" bestFit="true"/>
@@ -6505,7 +6406,7 @@
         <v>546.0</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W2" s="2" t="b">
         <v>0</v>
@@ -6546,22 +6447,22 @@
         <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>177</v>
@@ -6597,10 +6498,10 @@
         <v>93</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>785.0</v>
+        <v>840.0</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W3" s="2" t="b">
         <v>0</v>
@@ -6632,31 +6533,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>177</v>
@@ -6692,10 +6593,10 @@
         <v>93</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>245.0</v>
+        <v>619.0</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W4" s="2" t="b">
         <v>0</v>
@@ -6727,31 +6628,31 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>191</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>177</v>
@@ -6787,10 +6688,10 @@
         <v>93</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>156.0</v>
+        <v>369.0</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W5" s="2" t="b">
         <v>0</v>
@@ -6822,31 +6723,31 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>177</v>
@@ -6882,10 +6783,10 @@
         <v>93</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>318.0</v>
+        <v>603.0</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W6" s="2" t="b">
         <v>0</v>
@@ -6917,31 +6818,31 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>177</v>
@@ -6977,10 +6878,10 @@
         <v>93</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>56.0</v>
+        <v>802.0</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W7" s="2" t="b">
         <v>0</v>
@@ -7012,31 +6913,31 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>177</v>
@@ -7072,10 +6973,10 @@
         <v>93</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>596.0</v>
+        <v>39.0</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W8" s="2" t="b">
         <v>0</v>
@@ -7107,25 +7008,25 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
@@ -7167,10 +7068,10 @@
         <v>93</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>701.0</v>
+        <v>596.0</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W9" s="2" t="b">
         <v>0</v>
@@ -7211,19 +7112,19 @@
         <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>212</v>
@@ -7262,10 +7163,10 @@
         <v>93</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>77.0</v>
+        <v>468.0</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W10" s="2" t="b">
         <v>0</v>
@@ -7306,7 +7207,7 @@
         <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>215</v>
@@ -7315,7 +7216,7 @@
         <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
@@ -7357,25 +7258,25 @@
         <v>93</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>492.0</v>
+        <v>564.0</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="W11" s="2" t="b">
-        <v>0</v>
+        <v>0.0</v>
+      </c>
+      <c r="W11" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>93</v>
@@ -7401,10 +7302,10 @@
         <v>95</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>138</v>
+        <v>219</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -7413,10 +7314,10 @@
         <v>175</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>177</v>
@@ -7452,10 +7353,10 @@
         <v>93</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>623.0</v>
+        <v>618.0</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W12" s="2" t="b">
         <v>0</v>
@@ -7487,31 +7388,31 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>177</v>
@@ -7547,10 +7448,10 @@
         <v>93</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>789.0</v>
+        <v>444.0</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W13" s="2" t="b">
         <v>0</v>
@@ -7582,31 +7483,31 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>177</v>
@@ -7642,10 +7543,10 @@
         <v>93</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>206.0</v>
+        <v>294.0</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W14" s="2" t="b">
         <v>0</v>
@@ -7677,25 +7578,25 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
@@ -7737,10 +7638,10 @@
         <v>93</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>950.0</v>
+        <v>648.0</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W15" s="2" t="b">
         <v>0</v>
@@ -7784,19 +7685,19 @@
         <v>235</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>177</v>
@@ -7832,10 +7733,10 @@
         <v>93</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>995.0</v>
+        <v>625.0</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W16" s="2" t="b">
         <v>0</v>
@@ -7867,31 +7768,31 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>177</v>
@@ -7927,10 +7828,10 @@
         <v>93</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>530.0</v>
+        <v>55.0</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W17" s="2" t="b">
         <v>0</v>
@@ -7962,31 +7863,31 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>177</v>
@@ -8022,10 +7923,10 @@
         <v>93</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>529.0</v>
+        <v>601.0</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W18" s="2" t="b">
         <v>0</v>
@@ -8057,31 +7958,31 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>246</v>
+        <v>128</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>177</v>
@@ -8117,10 +8018,10 @@
         <v>93</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>715.0</v>
+        <v>530.0</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W19" s="2" t="b">
         <v>0</v>
@@ -8152,31 +8053,31 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>177</v>
@@ -8212,7 +8113,7 @@
         <v>93</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>516.0</v>
+        <v>481.0</v>
       </c>
       <c r="V20" s="2" t="n">
         <v>0.0</v>
@@ -8247,31 +8148,31 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>182</v>
+        <v>251</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>177</v>
@@ -8307,25 +8208,25 @@
         <v>93</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>43.0</v>
+        <v>944.0</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="W21" s="6" t="b">
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="W21" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>93</v>
@@ -8342,31 +8243,31 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>255</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>177</v>
@@ -8402,7 +8303,7 @@
         <v>93</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>445.0</v>
+        <v>711.0</v>
       </c>
       <c r="V22" s="2" t="n">
         <v>0.0</v>
@@ -8437,31 +8338,31 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>177</v>
@@ -8497,7 +8398,7 @@
         <v>93</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>289.0</v>
+        <v>455.0</v>
       </c>
       <c r="V23" s="2" t="n">
         <v>0.0</v>
@@ -8532,31 +8433,31 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>264</v>
+        <v>186</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>177</v>
@@ -8592,10 +8493,10 @@
         <v>93</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>229.0</v>
+        <v>871.0</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W24" s="2" t="b">
         <v>0</v>
@@ -8627,31 +8528,31 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>251</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>177</v>
@@ -8687,10 +8588,10 @@
         <v>93</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>915.0</v>
+        <v>411.0</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W25" s="2" t="b">
         <v>0</v>
@@ -8722,31 +8623,31 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>177</v>
@@ -8782,10 +8683,10 @@
         <v>93</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>466.0</v>
+        <v>118.0</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W26" s="2" t="b">
         <v>0</v>
@@ -8817,31 +8718,31 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>273</v>
+        <v>219</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>177</v>
@@ -8877,10 +8778,10 @@
         <v>93</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>388.0</v>
+        <v>991.0</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W27" s="2" t="b">
         <v>0</v>
@@ -8912,28 +8813,28 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>174</v>
+        <v>272</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>209</v>
@@ -8972,7 +8873,7 @@
         <v>93</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>32.0</v>
+        <v>704.0</v>
       </c>
       <c r="V28" s="2" t="n">
         <v>0.0</v>
@@ -9007,31 +8908,31 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>231</v>
+        <v>276</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>177</v>
@@ -9067,7 +8968,7 @@
         <v>93</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>558.0</v>
+        <v>355.0</v>
       </c>
       <c r="V29" s="2" t="n">
         <v>0.0</v>
@@ -9102,25 +9003,25 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>2.0</v>
@@ -9162,10 +9063,10 @@
         <v>93</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>119.0</v>
+        <v>917.0</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W30" s="2" t="b">
         <v>0</v>
@@ -9197,31 +9098,31 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>142</v>
+        <v>283</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>177</v>
@@ -9257,10 +9158,10 @@
         <v>93</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>838.0</v>
+        <v>32.0</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W31" s="2" t="b">
         <v>0</v>
@@ -9292,31 +9193,31 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>143</v>
+        <v>286</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>177</v>
@@ -9352,7 +9253,7 @@
         <v>93</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>734.0</v>
+        <v>183.0</v>
       </c>
       <c r="V32" s="2" t="n">
         <v>0.0</v>
@@ -9396,22 +9297,22 @@
         <v>95</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>144</v>
+        <v>289</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="H33" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>177</v>
@@ -9447,7 +9348,7 @@
         <v>93</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>888.0</v>
+        <v>956.0</v>
       </c>
       <c r="V33" s="2" t="n">
         <v>0.0</v>
@@ -9482,28 +9383,28 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>232</v>
@@ -9542,10 +9443,10 @@
         <v>93</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>421.0</v>
+        <v>902.0</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W34" s="2" t="b">
         <v>0</v>
@@ -9586,22 +9487,22 @@
         <v>95</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>295</v>
+        <v>132</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>177</v>
@@ -9637,10 +9538,10 @@
         <v>93</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>109.0</v>
+        <v>915.0</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W35" s="2" t="b">
         <v>0</v>
@@ -9672,31 +9573,31 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>299</v>
+        <v>196</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>296</v>
+        <v>174</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>177</v>
@@ -9732,7 +9633,7 @@
         <v>93</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>464.0</v>
+        <v>166.0</v>
       </c>
       <c r="V36" s="2" t="n">
         <v>0.0</v>
@@ -9767,31 +9668,31 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>302</v>
+        <v>135</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>181</v>
+        <v>299</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>303</v>
+        <v>93</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>177</v>
@@ -9827,10 +9728,10 @@
         <v>93</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>751.0</v>
+        <v>915.0</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W37" s="2" t="b">
         <v>0</v>
@@ -9875,7 +9776,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.4453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="14.7265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.83984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.22265625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.59375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.30078125" customWidth="true" bestFit="true"/>
@@ -9883,10 +9784,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2"/>
@@ -9895,16 +9796,16 @@
         <v>153</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -9944,7 +9845,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.0</v>
@@ -10091,7 +9992,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -10378,7 +10279,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -10424,8 +10325,8 @@
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>313</v>
+      <c r="C3" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -10916,8 +10817,8 @@
       <c r="B15" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>93</v>
+      <c r="C15" s="6" t="s">
+        <v>309</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>93</v>
@@ -11478,7 +11379,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -11519,13 +11420,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/36talks-12timeslots-5rooms.xlsx
@@ -35,9 +35,18 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
+</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0">
+      <text>
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
 </t>
       </text>
     </comment>
@@ -53,9 +62,18 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
+</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0">
+      <text>
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
 </t>
       </text>
     </comment>
@@ -69,11 +87,20 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0">
+    <comment ref="B3" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
+</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0">
+      <text>
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
 </t>
       </text>
     </comment>
@@ -87,11 +114,20 @@
     <author/>
   </authors>
   <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
+</t>
+      </text>
+    </comment>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
 </t>
       </text>
     </comment>
@@ -107,9 +143,23 @@
   <commentList>
     <comment ref="B3" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
+    -1650soft for 1 Popular talkss
+        S01
+</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0">
+      <text>
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
+    -2400soft for 1 Talk preferred room tagss
+    -1650soft for 1 Popular talkss
+        S24
 </t>
       </text>
     </comment>
@@ -125,9 +175,23 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
+    -1650soft for 1 Popular talkss
+        S01
+</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0">
+      <text>
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
+    -2400soft for 1 Talk preferred room tagss
+    -1650soft for 1 Popular talkss
+        S24
 </t>
       </text>
     </comment>
@@ -141,11 +205,20 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C15" authorId="0">
+    <comment ref="B6" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
+</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
 </t>
       </text>
     </comment>
@@ -159,11 +232,29 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0">
+    <comment ref="B3" authorId="0">
       <text>
-        <t xml:space="preserve">S09-Middleware: Debug enterprise Hibernate
-    Chad Jones
+        <t xml:space="preserve">S01-Cloud: Advanced containerized WildFly
+    Dan Jones
+-4050soft total
+</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0">
+      <text>
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
 PINNED BY USER
+-1650soft total
+</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0">
+      <text>
+        <t xml:space="preserve">S24-Culture, Security: Discover AI-driven jBPM
+    Jay Watt
+PINNED BY USER
+-1650soft total
 </t>
       </text>
     </comment>
@@ -172,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2752" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2822" uniqueCount="351">
   <si>
     <t>Conference name</t>
   </si>
@@ -255,6 +346,9 @@
     <t>Crowd control</t>
   </si>
   <si>
+    <t>0hard/0medium/0soft</t>
+  </si>
+  <si>
     <t>Penalty per talk with a non-zero crowd control risk that are not in paired with exactly one other such talk, per minute of either talk</t>
   </si>
   <si>
@@ -342,10 +436,7 @@
     <t>Audience type theme track conflict</t>
   </si>
   <si>
-    <t>0hard/0medium/0soft</t>
-  </si>
-  <si>
-    <t>Penalty per 2 talks with a common audience type, a common theme track and overlapping timeslotst, per overlapping minute</t>
+    <t>Penalty per 2 talks with a common audience type, a common theme track and overlapping timeslots, per overlapping minute</t>
   </si>
   <si>
     <t>Audience level diversity</t>
@@ -471,6 +562,9 @@
     <t>15:00</t>
   </si>
   <si>
+    <t>After lunch</t>
+  </si>
+  <si>
     <t>15:30</t>
   </si>
   <si>
@@ -513,544 +607,562 @@
     <t>R 1</t>
   </si>
   <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded, Large</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Talk type</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Theme track tags</t>
+  </si>
+  <si>
+    <t>Sector tags</t>
+  </si>
+  <si>
+    <t>Audience types</t>
+  </si>
+  <si>
+    <t>Audience level</t>
+  </si>
+  <si>
+    <t>Content tags</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Mutually exclusive talks tags</t>
+  </si>
+  <si>
+    <t>Prerequisite talks codes</t>
+  </si>
+  <si>
+    <t>Favorite count</t>
+  </si>
+  <si>
+    <t>Crowd control risk</t>
+  </si>
+  <si>
+    <t>Pinned by user</t>
+  </si>
+  <si>
+    <t>Timeslot day</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>Published Timeslot</t>
+  </si>
+  <si>
+    <t>Published Start</t>
+  </si>
+  <si>
+    <t>Published End</t>
+  </si>
+  <si>
+    <t>Published Room</t>
+  </si>
+  <si>
+    <t>S00</t>
+  </si>
+  <si>
+    <t>Hands on real-time OpenShift</t>
+  </si>
+  <si>
+    <t>Amy Cole, Beth Fox, Chad Green</t>
+  </si>
+  <si>
+    <t>IoT, Security</t>
+  </si>
+  <si>
+    <t>Business analysts</t>
+  </si>
+  <si>
+    <t>OpenShift, Kubernetes</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Programmers</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
     <t>Large, Recorded</t>
   </si>
   <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Talk type</t>
-  </si>
-  <si>
-    <t>Speakers</t>
-  </si>
-  <si>
-    <t>Theme track tags</t>
-  </si>
-  <si>
-    <t>Sector tags</t>
-  </si>
-  <si>
-    <t>Audience types</t>
-  </si>
-  <si>
-    <t>Audience level</t>
-  </si>
-  <si>
-    <t>Content tags</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Mutually exclusive talks tags</t>
-  </si>
-  <si>
-    <t>Prerequisite talks codes</t>
-  </si>
-  <si>
-    <t>Favorite count</t>
-  </si>
-  <si>
-    <t>Crowd control risk</t>
-  </si>
-  <si>
-    <t>Pinned by user</t>
-  </si>
-  <si>
-    <t>Timeslot day</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>Published Timeslot</t>
-  </si>
-  <si>
-    <t>Published Start</t>
-  </si>
-  <si>
-    <t>Published End</t>
-  </si>
-  <si>
-    <t>Published Room</t>
-  </si>
-  <si>
-    <t>S00</t>
-  </si>
-  <si>
-    <t>Hands on real-time OpenShift</t>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Elsa King, Flo Li</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Cloud, Middleware</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Hugo Rye, Ivy Smith</t>
+  </si>
+  <si>
+    <t>Security, Cloud</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
   </si>
   <si>
     <t>Security</t>
   </si>
   <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
     <t>Managers</t>
   </si>
   <si>
-    <t>OpenShift</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>Middleware, Cloud</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Chad Jones, Dan King</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Modern Web, IoT</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
+  </si>
+  <si>
+    <t>Modern Web, Cloud</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Cloud, Mobile</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>Beth Fox, Chad Green</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
   </si>
   <si>
     <t>Artificial Intelligence</t>
   </si>
   <si>
-    <t>Business analysts</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Chad Green, Dan Jones</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Programmers</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Elsa King, Flo Li</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Gus Poe, Hugo Rye</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>Culture, Big Data</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>Culture, Security</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>Beth Green, Chad Jones</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
   </si>
   <si>
     <t>Docker</t>
   </si>
   <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Dan King, Elsa Li</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Gus Rye, Hugo Smith</t>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>Security, Middleware</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
   </si>
   <si>
     <t>IoT</t>
   </si>
   <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>Jay Cole, Amy Green, Beth Jones, Chad King</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Ivy Smith, Jay Watt</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>Beth Green, Chad Jones</t>
-  </si>
-  <si>
-    <t>Modern Web, IoT</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Flo Poe, Gus Rye</t>
-  </si>
-  <si>
-    <t>Big Data, Culture</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>Hugo Smith, Ivy Watt</t>
-  </si>
-  <si>
-    <t>Culture, Middleware</t>
-  </si>
-  <si>
-    <t>Docker, Kubernetes</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable Hibernate</t>
-  </si>
-  <si>
-    <t>Jay Cole, Amy Green</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise GWT</t>
-  </si>
-  <si>
-    <t>Beth Jones, Chad King</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Errai</t>
-  </si>
-  <si>
-    <t>Dan Li, Amy Cole</t>
-  </si>
-  <si>
     <t>S31</t>
   </si>
   <si>
     <t>Understand mobile Angular</t>
   </si>
   <si>
-    <t>Beth Fox, Chad Green</t>
-  </si>
-  <si>
     <t>S32</t>
   </si>
   <si>
     <t>Applying modern Weld</t>
   </si>
   <si>
-    <t>Dan Jones, Elsa King</t>
+    <t>Ivy Watt, Jay Cole</t>
   </si>
   <si>
     <t>S33</t>
@@ -1059,25 +1171,31 @@
     <t>Grok distributed RestEasy</t>
   </si>
   <si>
+    <t>Amy Green, Beth Jones</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Big Data</t>
+  </si>
+  <si>
     <t>S34</t>
   </si>
   <si>
     <t>Troubleshooting reliable Android</t>
   </si>
   <si>
+    <t>Chad King, Dan Li</t>
+  </si>
+  <si>
     <t>S35</t>
   </si>
   <si>
     <t>Using secure Tensorflow</t>
   </si>
   <si>
-    <t>Modern Web, Middleware</t>
-  </si>
-  <si>
     <t>Score</t>
   </si>
   <si>
-    <t>-70init</t>
+    <t>-68init/-4050soft</t>
   </si>
   <si>
     <t>Count</t>
@@ -1095,14 +1213,21 @@
     <t>Total</t>
   </si>
   <si>
-    <t>S09: Debug enterprise Hibernate
-  Chad Jones</t>
+    <t>S24: Discover AI-driven jBPM
+  Jay Watt</t>
+  </si>
+  <si>
+    <t>S01: Advanced containerized WildFly
+  Dan Jones</t>
   </si>
   <si>
     <t>Speaker</t>
   </si>
   <si>
-    <t>S09 @ R 1</t>
+    <t>S01 @ R 5</t>
+  </si>
+  <si>
+    <t>S24 @ R 1</t>
   </si>
   <si>
     <t>Theme track tag</t>
@@ -1114,13 +1239,19 @@
     <t>Audience type</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>Content tag</t>
   </si>
   <si>
-    <t>S09 (level 3)</t>
+    <t>S01 (level 3)</t>
+  </si>
+  <si>
+    <t>S24 (level 1)</t>
   </si>
   <si>
     <t>Constraint name</t>
@@ -1168,14 +1299,27 @@
     <t>20soft</t>
   </si>
   <si>
+    <t>-2400soft</t>
+  </si>
+  <si>
     <t>10soft</t>
   </si>
   <si>
+    <t>-1650soft</t>
+  </si>
+  <si>
     <t>1soft</t>
   </si>
   <si>
-    <t>Debug enterprise Hibernate
-Chad Jones</t>
+    <t>S01, S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM
+Jay Watt</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly
+Dan Jones</t>
   </si>
 </sst>
 </file>
@@ -1434,9 +1578,9 @@
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.64453125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="149.2421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.74609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.7890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="170.40234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1452,7 +1596,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>30.0</v>
+        <v>15.0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -1551,175 +1695,175 @@
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
+      <c r="B12" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21"/>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="4" t="s">
         <v>56</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>57</v>
@@ -1730,7 +1874,7 @@
         <v>58</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>59</v>
@@ -1741,7 +1885,7 @@
         <v>60</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>61</v>
@@ -1763,7 +1907,7 @@
         <v>65</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>66</v>
@@ -1774,7 +1918,7 @@
         <v>67</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>68</v>
@@ -1785,7 +1929,7 @@
         <v>69</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>70</v>
@@ -1893,19 +2037,19 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1931,7 +2075,7 @@
         <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>93</v>
@@ -1951,43 +2095,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2005,22 +2149,22 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.1953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2046,7 +2190,7 @@
         <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>93</v>
@@ -2066,54 +2210,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2143,6 +2287,47 @@
         <v>93</v>
       </c>
       <c r="M3" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" ht="15.0" customHeight="true">
+      <c r="A4" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2162,22 +2347,22 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.4375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.3046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2203,7 +2388,7 @@
         <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>93</v>
@@ -2223,54 +2408,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2300,6 +2485,47 @@
         <v>93</v>
       </c>
       <c r="M3" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" ht="15.0" customHeight="true">
+      <c r="A4" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2319,22 +2545,22 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.78515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.9140625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.4609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2360,7 +2586,7 @@
         <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>93</v>
@@ -2380,54 +2606,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>315</v>
+        <v>327</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2457,6 +2683,47 @@
         <v>93</v>
       </c>
       <c r="M3" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" ht="15.0" customHeight="true">
+      <c r="A4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2479,19 +2746,19 @@
   <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="11.3046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2517,7 +2784,7 @@
         <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>93</v>
@@ -2537,54 +2804,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>93</v>
+        <v>319</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2633,58 +2900,58 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="17.34375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.65234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="1.0546875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="12.296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.9296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.6484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.7109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.98828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="9.8125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="1.1875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="13.73828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="14.6796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="n">
-        <v>-70.0</v>
+        <v>-68.0</v>
       </c>
     </row>
     <row r="5">
@@ -2692,13 +2959,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6">
@@ -2706,13 +2973,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7">
@@ -2720,13 +2987,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -2734,13 +3001,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2748,13 +3015,13 @@
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -2762,967 +3029,993 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42"/>
     <row r="43"/>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>323</v>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>323</v>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -3736,11 +4029,12 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.10546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="17.94140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="15.0" customWidth="true"/>
+    <col min="3" max="3" width="15.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3748,58 +4042,78 @@
         <v>89</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="2" ht="45.0" customHeight="true">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>93</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>333</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>93</v>
       </c>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>93</v>
       </c>
+      <c r="C7" s="10" t="s">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells>
+    <mergeCell ref="C2:C4"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -3814,42 +4128,42 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.1953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="17.3515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" ht="45.0" customHeight="true">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -3863,11 +4177,11 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.29296875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="5.1484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.14453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.3984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.32421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.87890625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.12890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3952,7 +4266,7 @@
         <v>92</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -3960,10 +4274,10 @@
         <v>89</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>95</v>
@@ -3977,10 +4291,10 @@
         <v>89</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>95</v>
@@ -3991,7 +4305,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>90</v>
@@ -4008,7 +4322,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>90</v>
@@ -4025,7 +4339,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>96</v>
@@ -4042,7 +4356,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>97</v>
@@ -